--- a/research/traditional_assets/database/data/germany/germany_education.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_education.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,8 +587,23 @@
           <t>Education</t>
         </is>
       </c>
+      <c r="G2">
+        <v>-0.2230540406544372</v>
+      </c>
+      <c r="H2">
+        <v>-0.2230540406544372</v>
+      </c>
+      <c r="I2">
+        <v>-0.3007718668708447</v>
+      </c>
+      <c r="J2">
+        <v>-0.3007718668708447</v>
+      </c>
       <c r="K2">
-        <v>0</v>
+        <v>-4.824</v>
+      </c>
+      <c r="L2">
+        <v>-0.2391670798215171</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -596,71 +611,77 @@
       <c r="N2">
         <v>0</v>
       </c>
+      <c r="O2">
+        <v>-0</v>
+      </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
+      <c r="R2">
+        <v>-0</v>
+      </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="V2">
-        <v>0.8559498956158663</v>
+        <v>0.1950043821209465</v>
       </c>
       <c r="X2">
-        <v>0.06179415614247579</v>
+        <v>0.09224377500002001</v>
       </c>
       <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0.831010658042949</v>
+        <v>9.073966110696855</v>
       </c>
       <c r="AB2">
-        <v>0.05397979674263979</v>
-      </c>
-      <c r="AC2">
-        <v>0.7770308613003093</v>
+        <v>0.08291418245558071</v>
       </c>
       <c r="AD2">
-        <v>0.8</v>
+        <v>1.881</v>
       </c>
       <c r="AE2">
-        <v>0.3598410909778831</v>
+        <v>0.9228427739246872</v>
       </c>
       <c r="AF2">
-        <v>1.159841090977883</v>
+        <v>2.803842773924687</v>
       </c>
       <c r="AG2">
-        <v>-2.940158909022117</v>
+        <v>-1.646157226075313</v>
       </c>
       <c r="AH2">
-        <v>0.1949364820409444</v>
+        <v>0.1094231961483128</v>
       </c>
       <c r="AI2">
-        <v>0.2013668559007016</v>
+        <v>0.1092100936589195</v>
       </c>
       <c r="AJ2">
-        <v>-1.589411611279463</v>
+        <v>-0.07774484979658648</v>
       </c>
       <c r="AK2">
-        <v>-1.77134963401222</v>
+        <v>-0.0775616952881765</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AN2">
-        <v>2.15633423180593</v>
+        <v>-0.671306209850107</v>
+      </c>
+      <c r="AO2">
+        <v>-329.578947368421</v>
       </c>
       <c r="AP2">
-        <v>-7.924956628091959</v>
+        <v>0.5874936567006827</v>
+      </c>
+      <c r="AQ2">
+        <v>-329.578947368421</v>
       </c>
     </row>
     <row r="3">
@@ -679,8 +700,23 @@
           <t>Education</t>
         </is>
       </c>
+      <c r="G3">
+        <v>0.001555869872701556</v>
+      </c>
+      <c r="H3">
+        <v>0.001555869872701556</v>
+      </c>
+      <c r="I3">
+        <v>0.02028733312801451</v>
+      </c>
+      <c r="J3">
+        <v>0.02028733312801451</v>
+      </c>
       <c r="K3">
-        <v>0</v>
+        <v>-0.044</v>
+      </c>
+      <c r="L3">
+        <v>-0.006223479490806223</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -688,71 +724,199 @@
       <c r="N3">
         <v>-0</v>
       </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
       <c r="P3">
         <v>-0</v>
       </c>
       <c r="Q3">
         <v>-0</v>
       </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.1</v>
+        <v>2.86</v>
       </c>
       <c r="V3">
-        <v>0.8559498956158663</v>
+        <v>0.6059322033898306</v>
+      </c>
+      <c r="W3">
+        <v>-0.009565217391304347</v>
       </c>
       <c r="X3">
-        <v>0.06179415614247579</v>
+        <v>0.0963470150923104</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1059122324836148</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.180611819664193</v>
       </c>
       <c r="AA3">
-        <v>0.831010658042949</v>
+        <v>0.06452613153642787</v>
       </c>
       <c r="AB3">
-        <v>0.05397979674263979</v>
+        <v>0.08099037203700434</v>
       </c>
       <c r="AC3">
-        <v>0.7770308613003093</v>
+        <v>-0.01646424050057646</v>
       </c>
       <c r="AD3">
-        <v>0.8</v>
+        <v>0.591</v>
       </c>
       <c r="AE3">
-        <v>0.3598410909778831</v>
+        <v>0.9228427739246872</v>
       </c>
       <c r="AF3">
-        <v>1.159841090977883</v>
+        <v>1.513842773924687</v>
       </c>
       <c r="AG3">
-        <v>-2.940158909022117</v>
+        <v>-1.346157226075313</v>
       </c>
       <c r="AH3">
-        <v>0.1949364820409444</v>
+        <v>0.2428426299516062</v>
       </c>
       <c r="AI3">
-        <v>0.2013668559007016</v>
+        <v>0.1970163651788855</v>
       </c>
       <c r="AJ3">
-        <v>-1.589411611279463</v>
+        <v>-0.3989982095429331</v>
       </c>
       <c r="AK3">
-        <v>-1.77134963401222</v>
+        <v>-0.2790632467028101</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="AN3">
-        <v>2.15633423180593</v>
+        <v>0.7796833773087071</v>
+      </c>
+      <c r="AO3">
+        <v>-4.333333333333333</v>
       </c>
       <c r="AP3">
-        <v>-7.924956628091959</v>
+        <v>-1.775933015930492</v>
+      </c>
+      <c r="AQ3">
+        <v>-4.333333333333333</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>123fahrschule SE (DB:123F)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-0.3442748091603053</v>
+      </c>
+      <c r="H4">
+        <v>-0.3442748091603053</v>
+      </c>
+      <c r="I4">
+        <v>-0.4740458015267175</v>
+      </c>
+      <c r="J4">
+        <v>-0.4740458015267175</v>
+      </c>
+      <c r="K4">
+        <v>-4.78</v>
+      </c>
+      <c r="L4">
+        <v>-0.3648854961832061</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1.59</v>
+      </c>
+      <c r="V4">
+        <v>0.08784530386740332</v>
+      </c>
+      <c r="X4">
+        <v>0.08814053490772963</v>
+      </c>
+      <c r="AB4">
+        <v>0.08483799287415711</v>
+      </c>
+      <c r="AD4">
+        <v>1.29</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>1.29</v>
+      </c>
+      <c r="AG4">
+        <v>-0.3</v>
+      </c>
+      <c r="AH4">
+        <v>0.0665291387313048</v>
+      </c>
+      <c r="AI4">
+        <v>0.07170650361311841</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.01685393258426967</v>
+      </c>
+      <c r="AK4">
+        <v>-0.01829268292682927</v>
+      </c>
+      <c r="AL4">
+        <v>0.007</v>
+      </c>
+      <c r="AM4">
+        <v>0.007</v>
+      </c>
+      <c r="AN4">
+        <v>-0.3623595505617977</v>
+      </c>
+      <c r="AO4">
+        <v>-887.1428571428571</v>
+      </c>
+      <c r="AP4">
+        <v>0.08426966292134833</v>
+      </c>
+      <c r="AQ4">
+        <v>-887.1428571428571</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_education.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_education.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.2230540406544372</v>
+        <v>-0.08524532297917403</v>
       </c>
       <c r="H2">
-        <v>-0.2230540406544372</v>
+        <v>-0.08524532297917403</v>
       </c>
       <c r="I2">
-        <v>-0.3007718668708447</v>
+        <v>-0.1635845629291175</v>
       </c>
       <c r="J2">
-        <v>-0.3007718668708447</v>
+        <v>-0.1635845629291175</v>
       </c>
       <c r="K2">
-        <v>-4.824</v>
+        <v>-4.088</v>
       </c>
       <c r="L2">
-        <v>-0.2391670798215171</v>
+        <v>-0.1442993293328627</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,61 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.45</v>
+        <v>2.721</v>
       </c>
       <c r="V2">
-        <v>0.1950043821209465</v>
+        <v>0.2099537037037037</v>
+      </c>
+      <c r="W2">
+        <v>-0.1248478731354147</v>
       </c>
       <c r="X2">
-        <v>0.09224377500002001</v>
+        <v>0.08098748343224157</v>
+      </c>
+      <c r="Y2">
+        <v>-0.2058353565676563</v>
       </c>
       <c r="Z2">
-        <v>9.073966110696855</v>
+        <v>2.361275415466659</v>
+      </c>
+      <c r="AA2">
+        <v>-0.3029203233262465</v>
       </c>
       <c r="AB2">
-        <v>0.08291418245558071</v>
+        <v>0.06990492675821477</v>
+      </c>
+      <c r="AC2">
+        <v>-0.3728252500844613</v>
       </c>
       <c r="AD2">
-        <v>1.881</v>
+        <v>3.563</v>
       </c>
       <c r="AE2">
-        <v>0.9228427739246872</v>
+        <v>0.5967533389094926</v>
       </c>
       <c r="AF2">
-        <v>2.803842773924687</v>
+        <v>4.159753338909493</v>
       </c>
       <c r="AG2">
-        <v>-1.646157226075313</v>
+        <v>1.438753338909493</v>
       </c>
       <c r="AH2">
-        <v>0.1094231961483128</v>
+        <v>0.2429797472289086</v>
       </c>
       <c r="AI2">
-        <v>0.1092100936589195</v>
+        <v>0.1488296976531311</v>
       </c>
       <c r="AJ2">
-        <v>-0.07774484979658648</v>
+        <v>0.09992207693575632</v>
       </c>
       <c r="AK2">
-        <v>-0.0775616952881765</v>
+        <v>0.05702831684079093</v>
       </c>
       <c r="AL2">
-        <v>0.019</v>
+        <v>0.037</v>
       </c>
       <c r="AM2">
-        <v>0.019</v>
+        <v>-0.002000000000000002</v>
       </c>
       <c r="AN2">
-        <v>-0.671306209850107</v>
+        <v>-11.83720930232558</v>
       </c>
       <c r="AO2">
-        <v>-329.578947368421</v>
+        <v>-130.9459459459459</v>
       </c>
       <c r="AP2">
-        <v>0.5874936567006827</v>
+        <v>-4.779911424948482</v>
       </c>
       <c r="AQ2">
-        <v>-329.578947368421</v>
+        <v>2422.499999999998</v>
       </c>
     </row>
     <row r="3">
@@ -701,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.001555869872701556</v>
+        <v>0.07540263543191801</v>
       </c>
       <c r="H3">
-        <v>0.001555869872701556</v>
+        <v>0.07540263543191801</v>
       </c>
       <c r="I3">
-        <v>0.02028733312801451</v>
+        <v>0.019860809988009</v>
       </c>
       <c r="J3">
-        <v>0.02028733312801451</v>
+        <v>0.019860809988009</v>
       </c>
       <c r="K3">
-        <v>-0.044</v>
+        <v>-0.048</v>
       </c>
       <c r="L3">
-        <v>-0.006223479490806223</v>
+        <v>-0.007027818448023426</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.86</v>
+        <v>2.46</v>
       </c>
       <c r="V3">
-        <v>0.6059322033898306</v>
+        <v>0.5913461538461539</v>
       </c>
       <c r="W3">
-        <v>-0.009565217391304347</v>
+        <v>-0.007779578606158834</v>
       </c>
       <c r="X3">
-        <v>0.0963470150923104</v>
+        <v>0.08053554903583909</v>
       </c>
       <c r="Y3">
-        <v>-0.1059122324836148</v>
+        <v>-0.08831512764199792</v>
       </c>
       <c r="Z3">
-        <v>3.180611819664193</v>
+        <v>1.518535919014175</v>
       </c>
       <c r="AA3">
-        <v>0.06452613153642787</v>
+        <v>0.03015935334750715</v>
       </c>
       <c r="AB3">
-        <v>0.08099037203700434</v>
+        <v>0.06935421831676478</v>
       </c>
       <c r="AC3">
-        <v>-0.01646424050057646</v>
+        <v>-0.03919486496925762</v>
       </c>
       <c r="AD3">
-        <v>0.591</v>
+        <v>0.633</v>
       </c>
       <c r="AE3">
-        <v>0.9228427739246872</v>
+        <v>0.5967533389094926</v>
       </c>
       <c r="AF3">
-        <v>1.513842773924687</v>
+        <v>1.229753338909493</v>
       </c>
       <c r="AG3">
-        <v>-1.346157226075313</v>
+        <v>-1.230246661090507</v>
       </c>
       <c r="AH3">
-        <v>0.2428426299516062</v>
+        <v>0.228165049786547</v>
       </c>
       <c r="AI3">
-        <v>0.1970163651788855</v>
+        <v>0.1751846937545719</v>
       </c>
       <c r="AJ3">
-        <v>-0.3989982095429331</v>
+        <v>-0.419914756901831</v>
       </c>
       <c r="AK3">
-        <v>-0.2790632467028101</v>
+        <v>-0.2698055288632635</v>
       </c>
       <c r="AL3">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="AM3">
-        <v>0.012</v>
+        <v>-0.029</v>
       </c>
       <c r="AN3">
-        <v>0.7796833773087071</v>
+        <v>0.9859813084112149</v>
       </c>
       <c r="AO3">
-        <v>-4.333333333333333</v>
+        <v>-7.5</v>
       </c>
       <c r="AP3">
-        <v>-1.775933015930492</v>
+        <v>-1.916272057773376</v>
       </c>
       <c r="AQ3">
-        <v>-4.333333333333333</v>
+        <v>2.586206896551724</v>
       </c>
     </row>
     <row r="4">
@@ -826,22 +838,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.3442748091603053</v>
+        <v>-0.1362790697674419</v>
       </c>
       <c r="H4">
-        <v>-0.3442748091603053</v>
+        <v>-0.1362790697674419</v>
       </c>
       <c r="I4">
-        <v>-0.4740458015267175</v>
+        <v>-0.221860465116279</v>
       </c>
       <c r="J4">
-        <v>-0.4740458015267175</v>
+        <v>-0.221860465116279</v>
       </c>
       <c r="K4">
-        <v>-4.78</v>
+        <v>-4.04</v>
       </c>
       <c r="L4">
-        <v>-0.3648854961832061</v>
+        <v>-0.187906976744186</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -865,58 +877,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.59</v>
+        <v>0.261</v>
       </c>
       <c r="V4">
-        <v>0.08784530386740332</v>
+        <v>0.02965909090909091</v>
+      </c>
+      <c r="W4">
+        <v>-0.2419161676646707</v>
       </c>
       <c r="X4">
-        <v>0.08814053490772963</v>
+        <v>0.08143941782864406</v>
+      </c>
+      <c r="Y4">
+        <v>-0.3233555854933147</v>
+      </c>
+      <c r="Z4">
+        <v>2.866666666666667</v>
+      </c>
+      <c r="AA4">
+        <v>-0.6360000000000001</v>
       </c>
       <c r="AB4">
-        <v>0.08483799287415711</v>
+        <v>0.07045563519966477</v>
+      </c>
+      <c r="AC4">
+        <v>-0.7064556351996649</v>
       </c>
       <c r="AD4">
-        <v>1.29</v>
+        <v>2.93</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.29</v>
+        <v>2.93</v>
       </c>
       <c r="AG4">
-        <v>-0.3</v>
+        <v>2.669</v>
       </c>
       <c r="AH4">
-        <v>0.0665291387313048</v>
+        <v>0.2497868712702472</v>
       </c>
       <c r="AI4">
-        <v>0.07170650361311841</v>
+        <v>0.1399904443382704</v>
       </c>
       <c r="AJ4">
-        <v>-0.01685393258426967</v>
+        <v>0.2327142732583486</v>
       </c>
       <c r="AK4">
-        <v>-0.01829268292682927</v>
+        <v>0.129130582031061</v>
       </c>
       <c r="AL4">
-        <v>0.007</v>
+        <v>0.027</v>
       </c>
       <c r="AM4">
-        <v>0.007</v>
+        <v>0.027</v>
       </c>
       <c r="AN4">
-        <v>-0.3623595505617977</v>
+        <v>-3.107104984093319</v>
       </c>
       <c r="AO4">
-        <v>-887.1428571428571</v>
+        <v>-176.6666666666667</v>
       </c>
       <c r="AP4">
-        <v>0.08426966292134833</v>
+        <v>-2.83032873806999</v>
       </c>
       <c r="AQ4">
-        <v>-887.1428571428571</v>
+        <v>-176.6666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_education.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_education.xlsx
@@ -1385,7 +1385,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1522,22 +1522,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07835024335450255</v>
+        <v>0.07814669262443903</v>
       </c>
       <c r="C2">
-        <v>4.600028646862037</v>
+        <v>4.559211368148654</v>
       </c>
       <c r="D2">
-        <v>3.991028646862037</v>
+        <v>3.997199163252815</v>
       </c>
       <c r="E2">
-        <v>-1.398779510416071</v>
+        <v>-1.351791715311911</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.04698779510416071</v>
       </c>
       <c r="G2">
         <v>0.609</v>
@@ -1558,28 +1558,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.002363486093739284</v>
       </c>
       <c r="N2">
-        <v>0.3540000000000001</v>
+        <v>0.3516365139062609</v>
       </c>
       <c r="O2">
-        <v>0.1062</v>
+        <v>0.1054909541718783</v>
       </c>
       <c r="P2">
-        <v>0.2478000000000001</v>
+        <v>0.2461455597343826</v>
       </c>
       <c r="Q2">
-        <v>0.6638000000000001</v>
+        <v>0.6621455597343826</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07835024335450255</v>
+        <v>0.07858039659034247</v>
       </c>
       <c r="T2">
-        <v>0.7517377218129921</v>
+        <v>0.7570530390379324</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>149.7787530621493</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1604,22 +1604,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07814669262443903</v>
+        <v>0.07794314189437554</v>
       </c>
       <c r="C3">
-        <v>4.559211368148654</v>
+        <v>4.518413199411728</v>
       </c>
       <c r="D3">
-        <v>3.997199163252815</v>
+        <v>4.00338878962005</v>
       </c>
       <c r="E3">
-        <v>-1.351791715311911</v>
+        <v>-1.30480392020775</v>
       </c>
       <c r="F3">
-        <v>0.04698779510416071</v>
+        <v>0.09397559020832143</v>
       </c>
       <c r="G3">
         <v>0.609</v>
@@ -1640,28 +1640,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M3">
-        <v>0.002363486093739284</v>
+        <v>0.004726972187478568</v>
       </c>
       <c r="N3">
-        <v>0.3516365139062609</v>
+        <v>0.3492730278125216</v>
       </c>
       <c r="O3">
-        <v>0.1054909541718783</v>
+        <v>0.1047819083437565</v>
       </c>
       <c r="P3">
-        <v>0.2461455597343826</v>
+        <v>0.2444911194687651</v>
       </c>
       <c r="Q3">
-        <v>0.6621455597343826</v>
+        <v>0.660491119468765</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07858039659034247</v>
+        <v>0.07881524683099544</v>
       </c>
       <c r="T3">
-        <v>0.7570530390379324</v>
+        <v>0.7624768321246063</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>149.7787530621493</v>
+        <v>74.88937653107467</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1686,22 +1686,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07794314189437554</v>
+        <v>0.07773959116431202</v>
       </c>
       <c r="C4">
-        <v>4.518413199411728</v>
+        <v>4.477634229563811</v>
       </c>
       <c r="D4">
-        <v>4.00338878962005</v>
+        <v>4.009597614876293</v>
       </c>
       <c r="E4">
-        <v>-1.30480392020775</v>
+        <v>-1.257816125103589</v>
       </c>
       <c r="F4">
-        <v>0.09397559020832143</v>
+        <v>0.1409633853124821</v>
       </c>
       <c r="G4">
         <v>0.609</v>
@@ -1722,28 +1722,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M4">
-        <v>0.004726972187478568</v>
+        <v>0.00709045828121785</v>
       </c>
       <c r="N4">
-        <v>0.3492730278125216</v>
+        <v>0.3469095417187823</v>
       </c>
       <c r="O4">
-        <v>0.1047819083437565</v>
+        <v>0.1040728625156347</v>
       </c>
       <c r="P4">
-        <v>0.2444911194687651</v>
+        <v>0.2428366792031476</v>
       </c>
       <c r="Q4">
-        <v>0.660491119468765</v>
+        <v>0.6588366792031476</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07881524683099544</v>
+        <v>0.07905493934465158</v>
       </c>
       <c r="T4">
-        <v>0.7624768321246063</v>
+        <v>0.7680124559965723</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>74.88937653107467</v>
+        <v>49.92625102071646</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1768,22 +1768,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07773959116431202</v>
+        <v>0.07753604043424851</v>
       </c>
       <c r="C5">
-        <v>4.477634229563811</v>
+        <v>4.436874548069887</v>
       </c>
       <c r="D5">
-        <v>4.009597614876293</v>
+        <v>4.015825728486529</v>
       </c>
       <c r="E5">
-        <v>-1.257816125103589</v>
+        <v>-1.210828329999428</v>
       </c>
       <c r="F5">
-        <v>0.1409633853124821</v>
+        <v>0.1879511804166429</v>
       </c>
       <c r="G5">
         <v>0.609</v>
@@ -1804,28 +1804,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M5">
-        <v>0.00709045828121785</v>
+        <v>0.009453944374957135</v>
       </c>
       <c r="N5">
-        <v>0.3469095417187823</v>
+        <v>0.344546055625043</v>
       </c>
       <c r="O5">
-        <v>0.1040728625156347</v>
+        <v>0.1033638166875129</v>
       </c>
       <c r="P5">
-        <v>0.2428366792031476</v>
+        <v>0.2411822389375301</v>
       </c>
       <c r="Q5">
-        <v>0.6588366792031476</v>
+        <v>0.6571822389375301</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07905493934465158</v>
+        <v>0.0792996254523422</v>
       </c>
       <c r="T5">
-        <v>0.7680124559965723</v>
+        <v>0.773663405365871</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>49.92625102071646</v>
+        <v>37.44468826553734</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1850,22 +1850,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07753604043424851</v>
+        <v>0.07733248970418501</v>
       </c>
       <c r="C6">
-        <v>4.436874548069887</v>
+        <v>4.396134244951668</v>
       </c>
       <c r="D6">
-        <v>4.015825728486529</v>
+        <v>4.022073220472471</v>
       </c>
       <c r="E6">
-        <v>-1.210828329999428</v>
+        <v>-1.163840534895268</v>
       </c>
       <c r="F6">
-        <v>0.1879511804166429</v>
+        <v>0.2349389755208036</v>
       </c>
       <c r="G6">
         <v>0.609</v>
@@ -1886,28 +1886,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M6">
-        <v>0.009453944374957135</v>
+        <v>0.01181743046869642</v>
       </c>
       <c r="N6">
-        <v>0.344546055625043</v>
+        <v>0.3421825695313037</v>
       </c>
       <c r="O6">
-        <v>0.1033638166875129</v>
+        <v>0.1026547708593911</v>
       </c>
       <c r="P6">
-        <v>0.2411822389375301</v>
+        <v>0.2395277986719126</v>
       </c>
       <c r="Q6">
-        <v>0.6571822389375301</v>
+        <v>0.6555277986719126</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0792996254523422</v>
+        <v>0.07954946284651054</v>
       </c>
       <c r="T6">
-        <v>0.773663405365871</v>
+        <v>0.7794333220903128</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.44468826553734</v>
+        <v>29.95575061242987</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1932,22 +1932,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07733248970418501</v>
+        <v>0.07712893897412151</v>
       </c>
       <c r="C7">
-        <v>4.396134244951668</v>
+        <v>4.355413410791933</v>
       </c>
       <c r="D7">
-        <v>4.022073220472471</v>
+        <v>4.028340181416898</v>
       </c>
       <c r="E7">
-        <v>-1.163840534895268</v>
+        <v>-1.116852739791107</v>
       </c>
       <c r="F7">
-        <v>0.2349389755208036</v>
+        <v>0.2819267706249643</v>
       </c>
       <c r="G7">
         <v>0.609</v>
@@ -1968,28 +1968,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M7">
-        <v>0.01181743046869642</v>
+        <v>0.0141809165624357</v>
       </c>
       <c r="N7">
-        <v>0.3421825695313037</v>
+        <v>0.3398190834375645</v>
       </c>
       <c r="O7">
-        <v>0.1026547708593911</v>
+        <v>0.1019457250312693</v>
       </c>
       <c r="P7">
-        <v>0.2395277986719126</v>
+        <v>0.2378733584062951</v>
       </c>
       <c r="Q7">
-        <v>0.6555277986719126</v>
+        <v>0.6538733584062951</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07954946284651054</v>
+        <v>0.0798046159299165</v>
       </c>
       <c r="T7">
-        <v>0.7794333220903128</v>
+        <v>0.785326003000381</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.95575061242987</v>
+        <v>24.96312551035822</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2014,22 +2014,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07712893897412151</v>
+        <v>0.07692538824405799</v>
       </c>
       <c r="C8">
-        <v>4.355413410791933</v>
+        <v>4.314712136738909</v>
       </c>
       <c r="D8">
-        <v>4.028340181416898</v>
+        <v>4.034626702468034</v>
       </c>
       <c r="E8">
-        <v>-1.116852739791107</v>
+        <v>-1.069864944686946</v>
       </c>
       <c r="F8">
-        <v>0.2819267706249642</v>
+        <v>0.328914565729125</v>
       </c>
       <c r="G8">
         <v>0.609</v>
@@ -2050,28 +2050,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M8">
-        <v>0.0141809165624357</v>
+        <v>0.01654440265617499</v>
       </c>
       <c r="N8">
-        <v>0.3398190834375645</v>
+        <v>0.3374555973438252</v>
       </c>
       <c r="O8">
-        <v>0.1019457250312693</v>
+        <v>0.1012366792031476</v>
       </c>
       <c r="P8">
-        <v>0.2378733584062951</v>
+        <v>0.2362189181406776</v>
       </c>
       <c r="Q8">
-        <v>0.6538733584062951</v>
+        <v>0.6522189181406777</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0798046159299165</v>
+        <v>0.08006525617640645</v>
       </c>
       <c r="T8">
-        <v>0.785326003000381</v>
+        <v>0.7913454082310961</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.96312551035823</v>
+        <v>21.3969647231642</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2096,22 +2096,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07692538824405799</v>
+        <v>0.0767218375139945</v>
       </c>
       <c r="C9">
-        <v>4.314712136738909</v>
+        <v>4.274030514510679</v>
       </c>
       <c r="D9">
-        <v>4.034626702468034</v>
+        <v>4.040932875343965</v>
       </c>
       <c r="E9">
-        <v>-1.069864944686946</v>
+        <v>-1.022877149582786</v>
       </c>
       <c r="F9">
-        <v>0.328914565729125</v>
+        <v>0.3759023608332857</v>
       </c>
       <c r="G9">
         <v>0.609</v>
@@ -2132,28 +2132,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M9">
-        <v>0.01654440265617499</v>
+        <v>0.01890788874991427</v>
       </c>
       <c r="N9">
-        <v>0.3374555973438251</v>
+        <v>0.3350921112500859</v>
       </c>
       <c r="O9">
-        <v>0.1012366792031475</v>
+        <v>0.1005276333750258</v>
       </c>
       <c r="P9">
-        <v>0.2362189181406776</v>
+        <v>0.2345644778750601</v>
       </c>
       <c r="Q9">
-        <v>0.6522189181406776</v>
+        <v>0.6505644778750601</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08006525617640645</v>
+        <v>0.08033156251521141</v>
       </c>
       <c r="T9">
-        <v>0.7913454082310961</v>
+        <v>0.7974956700972613</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.39696472316419</v>
+        <v>18.72234413276867</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2178,22 +2178,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0767218375139945</v>
+        <v>0.07651828678393099</v>
       </c>
       <c r="C10">
-        <v>4.274030514510679</v>
+        <v>4.233368636399656</v>
       </c>
       <c r="D10">
-        <v>4.040932875343965</v>
+        <v>4.047258792337103</v>
       </c>
       <c r="E10">
-        <v>-1.022877149582786</v>
+        <v>-0.975889354478625</v>
       </c>
       <c r="F10">
-        <v>0.3759023608332857</v>
+        <v>0.4228901559374464</v>
       </c>
       <c r="G10">
         <v>0.609</v>
@@ -2214,28 +2214,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M10">
-        <v>0.01890788874991427</v>
+        <v>0.02127137484365355</v>
       </c>
       <c r="N10">
-        <v>0.3350921112500859</v>
+        <v>0.3327286251563466</v>
       </c>
       <c r="O10">
-        <v>0.1005276333750258</v>
+        <v>0.09981858754690398</v>
       </c>
       <c r="P10">
-        <v>0.2345644778750601</v>
+        <v>0.2329100376094426</v>
       </c>
       <c r="Q10">
-        <v>0.6505644778750601</v>
+        <v>0.6489100376094425</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08033156251521141</v>
+        <v>0.0806037217405835</v>
       </c>
       <c r="T10">
-        <v>0.7974956700972613</v>
+        <v>0.8037811025538916</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.72234413276867</v>
+        <v>16.64208367357215</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2260,22 +2260,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07651828678393099</v>
+        <v>0.07631473605386747</v>
       </c>
       <c r="C11">
-        <v>4.233368636399656</v>
+        <v>4.192726595277079</v>
       </c>
       <c r="D11">
-        <v>4.047258792337103</v>
+        <v>4.053604546318685</v>
       </c>
       <c r="E11">
-        <v>-0.975889354478625</v>
+        <v>-0.9289015593744643</v>
       </c>
       <c r="F11">
-        <v>0.4228901559374464</v>
+        <v>0.4698779510416071</v>
       </c>
       <c r="G11">
         <v>0.609</v>
@@ -2296,28 +2296,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M11">
-        <v>0.02127137484365355</v>
+        <v>0.02363486093739283</v>
       </c>
       <c r="N11">
-        <v>0.3327286251563466</v>
+        <v>0.3303651390626073</v>
       </c>
       <c r="O11">
-        <v>0.09981858754690398</v>
+        <v>0.0991095417187822</v>
       </c>
       <c r="P11">
-        <v>0.2329100376094426</v>
+        <v>0.2312555973438251</v>
       </c>
       <c r="Q11">
-        <v>0.6489100376094425</v>
+        <v>0.6472555973438251</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0806037217405835</v>
+        <v>0.08088192894874163</v>
       </c>
       <c r="T11">
-        <v>0.8037811025538916</v>
+        <v>0.8102062112873359</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.64208367357215</v>
+        <v>14.97787530621494</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2342,22 +2342,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07631473605386747</v>
+        <v>0.07611118532380397</v>
       </c>
       <c r="C12">
-        <v>4.192726595277078</v>
+        <v>4.152104484597552</v>
       </c>
       <c r="D12">
-        <v>4.053604546318685</v>
+        <v>4.059970230743319</v>
       </c>
       <c r="E12">
-        <v>-0.9289015593744643</v>
+        <v>-0.8819137642703035</v>
       </c>
       <c r="F12">
-        <v>0.4698779510416071</v>
+        <v>0.5168657461457679</v>
       </c>
       <c r="G12">
         <v>0.609</v>
@@ -2378,28 +2378,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M12">
-        <v>0.02363486093739284</v>
+        <v>0.02599834703113212</v>
       </c>
       <c r="N12">
-        <v>0.3303651390626073</v>
+        <v>0.328001652968868</v>
       </c>
       <c r="O12">
-        <v>0.0991095417187822</v>
+        <v>0.0984004958906604</v>
       </c>
       <c r="P12">
-        <v>0.2312555973438251</v>
+        <v>0.2296011570782076</v>
       </c>
       <c r="Q12">
-        <v>0.6472555973438251</v>
+        <v>0.6456011570782076</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08088192894874163</v>
+        <v>0.08116638800427411</v>
       </c>
       <c r="T12">
-        <v>0.8102062112873359</v>
+        <v>0.8167757044867004</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.97787530621494</v>
+        <v>13.61625027837721</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2424,22 +2424,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07611118532380397</v>
+        <v>0.07603363459374046</v>
       </c>
       <c r="C13">
-        <v>4.152104484597552</v>
+        <v>4.107547212391147</v>
       </c>
       <c r="D13">
-        <v>4.059970230743319</v>
+        <v>4.062400753641075</v>
       </c>
       <c r="E13">
-        <v>-0.8819137642703035</v>
+        <v>-0.8349259691661429</v>
       </c>
       <c r="F13">
-        <v>0.5168657461457679</v>
+        <v>0.5638535412499285</v>
       </c>
       <c r="G13">
         <v>0.609</v>
@@ -2460,45 +2460,45 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M13">
-        <v>0.02599834703113212</v>
+        <v>0.0292076134367463</v>
       </c>
       <c r="N13">
-        <v>0.328001652968868</v>
+        <v>0.3247923865632539</v>
       </c>
       <c r="O13">
-        <v>0.0984004958906604</v>
+        <v>0.09743771596897616</v>
       </c>
       <c r="P13">
-        <v>0.2296011570782076</v>
+        <v>0.2273546705942777</v>
       </c>
       <c r="Q13">
-        <v>0.6456011570782076</v>
+        <v>0.6433546705942776</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08116638800427411</v>
+        <v>0.08145731203834143</v>
       </c>
       <c r="T13">
-        <v>0.8167757044867004</v>
+        <v>0.8234945043496869</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.61625027837721</v>
+        <v>12.1201275402608</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2506,22 +2506,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07603363459374046</v>
+        <v>0.07584058386367695</v>
       </c>
       <c r="C14">
-        <v>4.107547212391147</v>
+        <v>4.066622491505897</v>
       </c>
       <c r="D14">
-        <v>4.062400753641075</v>
+        <v>4.068463827859986</v>
       </c>
       <c r="E14">
-        <v>-0.8349259691661429</v>
+        <v>-0.7879381740619821</v>
       </c>
       <c r="F14">
-        <v>0.5638535412499285</v>
+        <v>0.6108413363540893</v>
       </c>
       <c r="G14">
         <v>0.609</v>
@@ -2542,28 +2542,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M14">
-        <v>0.0292076134367463</v>
+        <v>0.03164158122314183</v>
       </c>
       <c r="N14">
-        <v>0.3247923865632539</v>
+        <v>0.3223584187768583</v>
       </c>
       <c r="O14">
-        <v>0.09743771596897616</v>
+        <v>0.0967075256330575</v>
       </c>
       <c r="P14">
-        <v>0.2273546705942777</v>
+        <v>0.2256508931438008</v>
       </c>
       <c r="Q14">
-        <v>0.6433546705942776</v>
+        <v>0.6416508931438007</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08145731203834143</v>
+        <v>0.08175492398123788</v>
       </c>
       <c r="T14">
-        <v>0.8234945043496869</v>
+        <v>0.8303677593819373</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.1201275402608</v>
+        <v>11.18781003716381</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2588,22 +2588,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07584058386367695</v>
+        <v>0.07564753313361344</v>
       </c>
       <c r="C15">
-        <v>4.066622491505897</v>
+        <v>4.025715895772885</v>
       </c>
       <c r="D15">
-        <v>4.068463827859986</v>
+        <v>4.074545027231135</v>
       </c>
       <c r="E15">
-        <v>-0.7879381740619821</v>
+        <v>-0.7409503789578213</v>
       </c>
       <c r="F15">
-        <v>0.6108413363540893</v>
+        <v>0.6578291314582501</v>
       </c>
       <c r="G15">
         <v>0.609</v>
@@ -2624,28 +2624,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M15">
-        <v>0.03164158122314183</v>
+        <v>0.03407554900953735</v>
       </c>
       <c r="N15">
-        <v>0.3223584187768583</v>
+        <v>0.3199244509904628</v>
       </c>
       <c r="O15">
-        <v>0.0967075256330575</v>
+        <v>0.09597733529713884</v>
       </c>
       <c r="P15">
-        <v>0.2256508931438008</v>
+        <v>0.223947115693324</v>
       </c>
       <c r="Q15">
-        <v>0.6416508931438007</v>
+        <v>0.639947115693324</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08175492398123788</v>
+        <v>0.08205945713210866</v>
       </c>
       <c r="T15">
-        <v>0.8303677593819373</v>
+        <v>0.8374008575544726</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.18781003716381</v>
+        <v>10.38868074879497</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2670,22 +2670,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07564753313361344</v>
+        <v>0.07563298240354994</v>
       </c>
       <c r="C16">
-        <v>4.025715895772885</v>
+        <v>3.979187193139857</v>
       </c>
       <c r="D16">
-        <v>4.074545027231135</v>
+        <v>4.075004119702268</v>
       </c>
       <c r="E16">
-        <v>-0.7409503789578213</v>
+        <v>-0.6939625838536606</v>
       </c>
       <c r="F16">
-        <v>0.6578291314582501</v>
+        <v>0.7048169265624108</v>
       </c>
       <c r="G16">
         <v>0.609</v>
@@ -2706,45 +2706,45 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M16">
-        <v>0.03407554900953735</v>
+        <v>0.03770770557108898</v>
       </c>
       <c r="N16">
-        <v>0.3199244509904628</v>
+        <v>0.3162922944289112</v>
       </c>
       <c r="O16">
-        <v>0.09597733529713884</v>
+        <v>0.09488768832867335</v>
       </c>
       <c r="P16">
-        <v>0.223947115693324</v>
+        <v>0.2214046061002378</v>
       </c>
       <c r="Q16">
-        <v>0.639947115693324</v>
+        <v>0.6374046061002379</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08205945713210866</v>
+        <v>0.08237115576888229</v>
       </c>
       <c r="T16">
-        <v>0.8374008575544726</v>
+        <v>0.8445994403898912</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.38868074879497</v>
+        <v>9.388001593802008</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2752,22 +2752,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07563298240354994</v>
+        <v>0.07545183167348643</v>
       </c>
       <c r="C17">
-        <v>3.979187193139857</v>
+        <v>3.937923587956886</v>
       </c>
       <c r="D17">
-        <v>4.075004119702268</v>
+        <v>4.080728309623457</v>
       </c>
       <c r="E17">
-        <v>-0.6939625838536607</v>
+        <v>-0.6469747887495</v>
       </c>
       <c r="F17">
-        <v>0.7048169265624107</v>
+        <v>0.7518047216665714</v>
       </c>
       <c r="G17">
         <v>0.609</v>
@@ -2788,28 +2788,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M17">
-        <v>0.03770770557108897</v>
+        <v>0.04022155260916157</v>
       </c>
       <c r="N17">
-        <v>0.3162922944289112</v>
+        <v>0.3137784473908386</v>
       </c>
       <c r="O17">
-        <v>0.09488768832867335</v>
+        <v>0.09413353421725158</v>
       </c>
       <c r="P17">
-        <v>0.2214046061002378</v>
+        <v>0.219644913173587</v>
       </c>
       <c r="Q17">
-        <v>0.6374046061002379</v>
+        <v>0.6356449131735871</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08237115576888229</v>
+        <v>0.08269027580176956</v>
       </c>
       <c r="T17">
-        <v>0.8445994403898912</v>
+        <v>0.8519694180547244</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.388001593802009</v>
+        <v>8.801251494189383</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2834,22 +2834,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07545183167348643</v>
+        <v>0.07527068094342292</v>
       </c>
       <c r="C18">
-        <v>3.937923587956886</v>
+        <v>3.896676087023717</v>
       </c>
       <c r="D18">
-        <v>4.080728309623457</v>
+        <v>4.086468603794449</v>
       </c>
       <c r="E18">
-        <v>-0.6469747887495</v>
+        <v>-0.5999869936453393</v>
       </c>
       <c r="F18">
-        <v>0.7518047216665714</v>
+        <v>0.7987925167707322</v>
       </c>
       <c r="G18">
         <v>0.609</v>
@@ -2870,28 +2870,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M18">
-        <v>0.04022155260916157</v>
+        <v>0.04273539964723417</v>
       </c>
       <c r="N18">
-        <v>0.3137784473908386</v>
+        <v>0.311264600352766</v>
       </c>
       <c r="O18">
-        <v>0.09413353421725158</v>
+        <v>0.09337938010582979</v>
       </c>
       <c r="P18">
-        <v>0.219644913173587</v>
+        <v>0.2178852202469362</v>
       </c>
       <c r="Q18">
-        <v>0.6356449131735871</v>
+        <v>0.6338852202469362</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08269027580176956</v>
+        <v>0.08301708547400352</v>
       </c>
       <c r="T18">
-        <v>0.8519694180547244</v>
+        <v>0.8595169855428068</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.801251494189383</v>
+        <v>8.283530818060596</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2916,22 +2916,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07527068094342292</v>
+        <v>0.07508953021335942</v>
       </c>
       <c r="C19">
-        <v>3.896676087023717</v>
+        <v>3.855444758396844</v>
       </c>
       <c r="D19">
-        <v>4.086468603794449</v>
+        <v>4.092225070271737</v>
       </c>
       <c r="E19">
-        <v>-0.5999869936453393</v>
+        <v>-0.5529991985411785</v>
       </c>
       <c r="F19">
-        <v>0.7987925167707322</v>
+        <v>0.8457803118748929</v>
       </c>
       <c r="G19">
         <v>0.609</v>
@@ -2952,28 +2952,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M19">
-        <v>0.04273539964723417</v>
+        <v>0.04524924668530677</v>
       </c>
       <c r="N19">
-        <v>0.311264600352766</v>
+        <v>0.3087507533146934</v>
       </c>
       <c r="O19">
-        <v>0.09337938010582979</v>
+        <v>0.09262522599440801</v>
       </c>
       <c r="P19">
-        <v>0.2178852202469362</v>
+        <v>0.2161255273202854</v>
       </c>
       <c r="Q19">
-        <v>0.6338852202469362</v>
+        <v>0.6321255273202854</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08301708547400352</v>
+        <v>0.08335186611385295</v>
       </c>
       <c r="T19">
-        <v>0.8595169855428068</v>
+        <v>0.8672486400427933</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.283530818060596</v>
+        <v>7.823334661501673</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2998,22 +2998,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07508953021335943</v>
+        <v>0.07501477948329592</v>
       </c>
       <c r="C20">
-        <v>3.855444758396843</v>
+        <v>3.810837063234631</v>
       </c>
       <c r="D20">
-        <v>4.092225070271736</v>
+        <v>4.094605170213685</v>
       </c>
       <c r="E20">
-        <v>-0.5529991985411786</v>
+        <v>-0.5060114034370179</v>
       </c>
       <c r="F20">
-        <v>0.8457803118748928</v>
+        <v>0.8927681069790535</v>
       </c>
       <c r="G20">
         <v>0.609</v>
@@ -3034,45 +3034,45 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M20">
-        <v>0.04524924668530676</v>
+        <v>0.04847730820896261</v>
       </c>
       <c r="N20">
-        <v>0.3087507533146934</v>
+        <v>0.3055226917910375</v>
       </c>
       <c r="O20">
-        <v>0.09262522599440801</v>
+        <v>0.09165680753731126</v>
       </c>
       <c r="P20">
-        <v>0.2161255273202854</v>
+        <v>0.2138658842537263</v>
       </c>
       <c r="Q20">
-        <v>0.6321255273202854</v>
+        <v>0.6298658842537262</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08335186611385295</v>
+        <v>0.08369491294234063</v>
       </c>
       <c r="T20">
-        <v>0.8672486400427933</v>
+        <v>0.8751711995921624</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.823334661501674</v>
+        <v>7.302385653800632</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3080,22 +3080,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07501477948329592</v>
+        <v>0.0748392287532324</v>
       </c>
       <c r="C21">
-        <v>3.810837063234631</v>
+        <v>3.769449790389007</v>
       </c>
       <c r="D21">
-        <v>4.094605170213685</v>
+        <v>4.100205692472222</v>
       </c>
       <c r="E21">
-        <v>-0.5060114034370179</v>
+        <v>-0.4590236083328572</v>
       </c>
       <c r="F21">
-        <v>0.8927681069790535</v>
+        <v>0.9397559020832142</v>
       </c>
       <c r="G21">
         <v>0.609</v>
@@ -3116,28 +3116,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M21">
-        <v>0.04847730820896261</v>
+        <v>0.05102874548311853</v>
       </c>
       <c r="N21">
-        <v>0.3055226917910375</v>
+        <v>0.3029712545168816</v>
       </c>
       <c r="O21">
-        <v>0.09165680753731126</v>
+        <v>0.09089137635506449</v>
       </c>
       <c r="P21">
-        <v>0.2138658842537263</v>
+        <v>0.2120798781618171</v>
       </c>
       <c r="Q21">
-        <v>0.6298658842537262</v>
+        <v>0.6280798781618171</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08369491294234063</v>
+        <v>0.0840465359415405</v>
       </c>
       <c r="T21">
-        <v>0.8751711995921624</v>
+        <v>0.8832918231302658</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.302385653800632</v>
+        <v>6.9372663711106</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3162,22 +3162,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0748392287532324</v>
+        <v>0.07466367802316889</v>
       </c>
       <c r="C22">
-        <v>3.769449790389007</v>
+        <v>3.728077859100689</v>
       </c>
       <c r="D22">
-        <v>4.100205692472222</v>
+        <v>4.105821556288064</v>
       </c>
       <c r="E22">
-        <v>-0.4590236083328572</v>
+        <v>-0.4120358132286963</v>
       </c>
       <c r="F22">
-        <v>0.9397559020832142</v>
+        <v>0.9867436971873751</v>
       </c>
       <c r="G22">
         <v>0.609</v>
@@ -3198,28 +3198,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M22">
-        <v>0.05102874548311853</v>
+        <v>0.05358018275727447</v>
       </c>
       <c r="N22">
-        <v>0.3029712545168816</v>
+        <v>0.3004198172427257</v>
       </c>
       <c r="O22">
-        <v>0.09089137635506449</v>
+        <v>0.0901259451728177</v>
       </c>
       <c r="P22">
-        <v>0.2120798781618171</v>
+        <v>0.210293872069908</v>
       </c>
       <c r="Q22">
-        <v>0.6280798781618171</v>
+        <v>0.6262938720699081</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0840465359415405</v>
+        <v>0.08440706078882138</v>
       </c>
       <c r="T22">
-        <v>0.8832918231302658</v>
+        <v>0.891618032074397</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.9372663711106</v>
+        <v>6.606920353438666</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3244,22 +3244,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07466367802316889</v>
+        <v>0.07448812729310539</v>
       </c>
       <c r="C23">
-        <v>3.728077859100689</v>
+        <v>3.686721332494021</v>
       </c>
       <c r="D23">
-        <v>4.105821556288064</v>
+        <v>4.111452824785557</v>
       </c>
       <c r="E23">
-        <v>-0.4120358132286965</v>
+        <v>-0.3650480181245357</v>
       </c>
       <c r="F23">
-        <v>0.9867436971873749</v>
+        <v>1.033731492291536</v>
       </c>
       <c r="G23">
         <v>0.609</v>
@@ -3280,28 +3280,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M23">
-        <v>0.05358018275727446</v>
+        <v>0.05613162003143039</v>
       </c>
       <c r="N23">
-        <v>0.3004198172427257</v>
+        <v>0.2978683799685697</v>
       </c>
       <c r="O23">
-        <v>0.0901259451728177</v>
+        <v>0.08936051399057092</v>
       </c>
       <c r="P23">
-        <v>0.210293872069908</v>
+        <v>0.2085078659779988</v>
       </c>
       <c r="Q23">
-        <v>0.6262938720699081</v>
+        <v>0.6245078659779988</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08440706078882138</v>
+        <v>0.08477682986295562</v>
       </c>
       <c r="T23">
-        <v>0.8916180320743969</v>
+        <v>0.9001577335555573</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.606920353438668</v>
+        <v>6.306605791918726</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3326,22 +3326,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07448812729310539</v>
+        <v>0.07447357656304188</v>
       </c>
       <c r="C24">
-        <v>3.686721332494021</v>
+        <v>3.640200985053925</v>
       </c>
       <c r="D24">
-        <v>4.111452824785557</v>
+        <v>4.111920272449622</v>
       </c>
       <c r="E24">
-        <v>-0.3650480181245357</v>
+        <v>-0.3180602230203751</v>
       </c>
       <c r="F24">
-        <v>1.033731492291536</v>
+        <v>1.080719287395696</v>
       </c>
       <c r="G24">
         <v>0.609</v>
@@ -3362,45 +3362,45 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M24">
-        <v>0.05613162003143039</v>
+        <v>0.05976377659298201</v>
       </c>
       <c r="N24">
-        <v>0.2978683799685697</v>
+        <v>0.2942362234070182</v>
       </c>
       <c r="O24">
-        <v>0.08936051399057092</v>
+        <v>0.08827086702210545</v>
       </c>
       <c r="P24">
-        <v>0.2085078659779988</v>
+        <v>0.2059653563849127</v>
       </c>
       <c r="Q24">
-        <v>0.6245078659779988</v>
+        <v>0.6219653563849127</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08477682986295562</v>
+        <v>0.08515620332862581</v>
       </c>
       <c r="T24">
-        <v>0.9001577335555573</v>
+        <v>0.9089192454647995</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.306605791918726</v>
+        <v>5.923320448955195</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3408,22 +3408,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07447357656304188</v>
+        <v>0.07430502583297838</v>
       </c>
       <c r="C25">
-        <v>3.640200985053925</v>
+        <v>3.598635702446362</v>
       </c>
       <c r="D25">
-        <v>4.111920272449622</v>
+        <v>4.117342784946219</v>
       </c>
       <c r="E25">
-        <v>-0.3180602230203751</v>
+        <v>-0.2710724279162142</v>
       </c>
       <c r="F25">
-        <v>1.080719287395696</v>
+        <v>1.127707082499857</v>
       </c>
       <c r="G25">
         <v>0.609</v>
@@ -3444,28 +3444,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M25">
-        <v>0.05976377659298201</v>
+        <v>0.06236220166224211</v>
       </c>
       <c r="N25">
-        <v>0.2942362234070182</v>
+        <v>0.291637798337758</v>
       </c>
       <c r="O25">
-        <v>0.08827086702210545</v>
+        <v>0.08749133950132741</v>
       </c>
       <c r="P25">
-        <v>0.2059653563849127</v>
+        <v>0.2041464588364306</v>
       </c>
       <c r="Q25">
-        <v>0.6219653563849127</v>
+        <v>0.6201464588364306</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08515620332862581</v>
+        <v>0.08554556030655049</v>
       </c>
       <c r="T25">
-        <v>0.9089192454647995</v>
+        <v>0.9179113234769167</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.923320448955195</v>
+        <v>5.676515430248728</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3490,22 +3490,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07430502583297838</v>
+        <v>0.07413647510291488</v>
       </c>
       <c r="C26">
-        <v>3.598635702446362</v>
+        <v>3.557084740383212</v>
       </c>
       <c r="D26">
-        <v>4.117342784946219</v>
+        <v>4.12277961798723</v>
       </c>
       <c r="E26">
-        <v>-0.2710724279162144</v>
+        <v>-0.2240846328120536</v>
       </c>
       <c r="F26">
-        <v>1.127707082499857</v>
+        <v>1.174694877604018</v>
       </c>
       <c r="G26">
         <v>0.609</v>
@@ -3526,28 +3526,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M26">
-        <v>0.06236220166224209</v>
+        <v>0.06496062673150219</v>
       </c>
       <c r="N26">
-        <v>0.291637798337758</v>
+        <v>0.2890393732684979</v>
       </c>
       <c r="O26">
-        <v>0.08749133950132741</v>
+        <v>0.08671181198054938</v>
       </c>
       <c r="P26">
-        <v>0.2041464588364306</v>
+        <v>0.2023275612879485</v>
       </c>
       <c r="Q26">
-        <v>0.6201464588364306</v>
+        <v>0.6183275612879485</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08554556030655049</v>
+        <v>0.08594530013721982</v>
       </c>
       <c r="T26">
-        <v>0.9179113234769167</v>
+        <v>0.9271431902360237</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.676515430248728</v>
+        <v>5.449454813038779</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3572,22 +3572,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07413647510291488</v>
+        <v>0.07396792437285135</v>
       </c>
       <c r="C27">
-        <v>3.557084740383212</v>
+        <v>3.515548155669088</v>
       </c>
       <c r="D27">
-        <v>4.12277961798723</v>
+        <v>4.128230828377267</v>
       </c>
       <c r="E27">
-        <v>-0.2240846328120536</v>
+        <v>-0.1770968377078928</v>
       </c>
       <c r="F27">
-        <v>1.174694877604018</v>
+        <v>1.221682672708179</v>
       </c>
       <c r="G27">
         <v>0.609</v>
@@ -3608,28 +3608,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M27">
-        <v>0.06496062673150219</v>
+        <v>0.06755905180076228</v>
       </c>
       <c r="N27">
-        <v>0.2890393732684979</v>
+        <v>0.2864409481992379</v>
       </c>
       <c r="O27">
-        <v>0.08671181198054938</v>
+        <v>0.08593228445977136</v>
       </c>
       <c r="P27">
-        <v>0.2023275612879485</v>
+        <v>0.2005086637394665</v>
       </c>
       <c r="Q27">
-        <v>0.6183275612879485</v>
+        <v>0.6165086637394666</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08594530013721982</v>
+        <v>0.08635584374709643</v>
       </c>
       <c r="T27">
-        <v>0.9271431902360237</v>
+        <v>0.9366245669075388</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.449454813038779</v>
+        <v>5.239860397152671</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3654,22 +3654,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07396792437285135</v>
+        <v>0.07379937364278785</v>
       </c>
       <c r="C28">
-        <v>3.515548155669088</v>
+        <v>3.474026005409432</v>
       </c>
       <c r="D28">
-        <v>4.128230828377267</v>
+        <v>4.133696473221772</v>
       </c>
       <c r="E28">
-        <v>-0.1770968377078928</v>
+        <v>-0.1301090426037321</v>
       </c>
       <c r="F28">
-        <v>1.221682672708179</v>
+        <v>1.268670467812339</v>
       </c>
       <c r="G28">
         <v>0.609</v>
@@ -3690,28 +3690,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M28">
-        <v>0.06755905180076228</v>
+        <v>0.07015747687002237</v>
       </c>
       <c r="N28">
-        <v>0.2864409481992379</v>
+        <v>0.2838425231299778</v>
       </c>
       <c r="O28">
-        <v>0.08593228445977136</v>
+        <v>0.08515275693899332</v>
       </c>
       <c r="P28">
-        <v>0.2005086637394665</v>
+        <v>0.1986897661909844</v>
       </c>
       <c r="Q28">
-        <v>0.6165086637394666</v>
+        <v>0.6146897661909845</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08635584374709643</v>
+        <v>0.08677763512710665</v>
       </c>
       <c r="T28">
-        <v>0.9366245669075388</v>
+        <v>0.9463657073234792</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.239860397152671</v>
+        <v>5.045791493554424</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3736,22 +3736,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07379937364278785</v>
+        <v>0.07363082291272433</v>
       </c>
       <c r="C29">
-        <v>3.474026005409432</v>
+        <v>3.432518347012513</v>
       </c>
       <c r="D29">
-        <v>4.133696473221772</v>
+        <v>4.139176609929013</v>
       </c>
       <c r="E29">
-        <v>-0.1301090426037321</v>
+        <v>-0.08312124749957128</v>
       </c>
       <c r="F29">
-        <v>1.268670467812339</v>
+        <v>1.3156582629165</v>
       </c>
       <c r="G29">
         <v>0.609</v>
@@ -3772,28 +3772,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M29">
-        <v>0.07015747687002237</v>
+        <v>0.07275590193928246</v>
       </c>
       <c r="N29">
-        <v>0.2838425231299778</v>
+        <v>0.2812440980607177</v>
       </c>
       <c r="O29">
-        <v>0.08515275693899332</v>
+        <v>0.0843732294182153</v>
       </c>
       <c r="P29">
-        <v>0.1986897661909844</v>
+        <v>0.1968708686425024</v>
       </c>
       <c r="Q29">
-        <v>0.6146897661909845</v>
+        <v>0.6128708686425024</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08677763512710665</v>
+        <v>0.08721114293433935</v>
       </c>
       <c r="T29">
-        <v>0.9463657073234792</v>
+        <v>0.9563774349731955</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.045791493554424</v>
+        <v>4.865584654498909</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3818,22 +3818,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07363082291272433</v>
+        <v>0.07346227218266084</v>
       </c>
       <c r="C30">
-        <v>3.432518347012513</v>
+        <v>3.39102523819143</v>
       </c>
       <c r="D30">
-        <v>4.139176609929013</v>
+        <v>4.144671296212091</v>
       </c>
       <c r="E30">
-        <v>-0.08312124749957128</v>
+        <v>-0.03613345239541066</v>
       </c>
       <c r="F30">
-        <v>1.3156582629165</v>
+        <v>1.362646058020661</v>
       </c>
       <c r="G30">
         <v>0.609</v>
@@ -3854,28 +3854,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M30">
-        <v>0.07275590193928246</v>
+        <v>0.07535432700854254</v>
       </c>
       <c r="N30">
-        <v>0.2812440980607177</v>
+        <v>0.2786456729914576</v>
       </c>
       <c r="O30">
-        <v>0.0843732294182153</v>
+        <v>0.08359370189743727</v>
       </c>
       <c r="P30">
-        <v>0.1968708686425024</v>
+        <v>0.1950519710940203</v>
       </c>
       <c r="Q30">
-        <v>0.6128708686425024</v>
+        <v>0.6110519710940203</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08721114293433935</v>
+        <v>0.08765686222909977</v>
       </c>
       <c r="T30">
-        <v>0.9563774349731955</v>
+        <v>0.9666711831200872</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.865584654498909</v>
+        <v>4.697805873309292</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3900,22 +3900,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07346227218266084</v>
+        <v>0.07329372145259733</v>
       </c>
       <c r="C31">
-        <v>3.391025238191431</v>
+        <v>3.349546736966146</v>
       </c>
       <c r="D31">
-        <v>4.144671296212091</v>
+        <v>4.150180590090968</v>
       </c>
       <c r="E31">
-        <v>-0.03613345239541088</v>
+        <v>0.01085434270874996</v>
       </c>
       <c r="F31">
-        <v>1.362646058020661</v>
+        <v>1.409633853124821</v>
       </c>
       <c r="G31">
         <v>0.609</v>
@@ -3936,28 +3936,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M31">
-        <v>0.07535432700854253</v>
+        <v>0.07795275207780263</v>
       </c>
       <c r="N31">
-        <v>0.2786456729914576</v>
+        <v>0.2760472479221975</v>
       </c>
       <c r="O31">
-        <v>0.08359370189743727</v>
+        <v>0.08281417437665926</v>
       </c>
       <c r="P31">
-        <v>0.1950519710940203</v>
+        <v>0.1932330735455383</v>
       </c>
       <c r="Q31">
-        <v>0.6110519710940203</v>
+        <v>0.6092330735455382</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08765686222909977</v>
+        <v>0.08811531636085332</v>
       </c>
       <c r="T31">
-        <v>0.9666711831200872</v>
+        <v>0.9772590383568899</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.697805873309292</v>
+        <v>4.541212344198982</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3982,22 +3982,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07329372145259733</v>
+        <v>0.07366767072253382</v>
       </c>
       <c r="C32">
-        <v>3.349546736966146</v>
+        <v>3.290355677931463</v>
       </c>
       <c r="D32">
-        <v>4.150180590090968</v>
+        <v>4.137977326160445</v>
       </c>
       <c r="E32">
-        <v>0.01085434270874996</v>
+        <v>0.05784213781291059</v>
       </c>
       <c r="F32">
-        <v>1.409633853124821</v>
+        <v>1.456621648228982</v>
       </c>
       <c r="G32">
         <v>0.609</v>
@@ -4018,45 +4018,45 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M32">
-        <v>0.07795275207780263</v>
+        <v>0.08419273126763517</v>
       </c>
       <c r="N32">
-        <v>0.2760472479221975</v>
+        <v>0.269807268732365</v>
       </c>
       <c r="O32">
-        <v>0.08281417437665926</v>
+        <v>0.08094218061970949</v>
       </c>
       <c r="P32">
-        <v>0.1932330735455383</v>
+        <v>0.1888650881126555</v>
       </c>
       <c r="Q32">
-        <v>0.6092330735455382</v>
+        <v>0.6048650881126555</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08811531636085332</v>
+        <v>0.08858705901816495</v>
       </c>
       <c r="T32">
-        <v>0.9772590383568899</v>
+        <v>0.9881537879483824</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.541212344198982</v>
+        <v>4.204638508218613</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4064,22 +4064,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07366767072253382</v>
+        <v>0.07351661999247031</v>
       </c>
       <c r="C33">
-        <v>3.290355677931463</v>
+        <v>3.248288543166115</v>
       </c>
       <c r="D33">
-        <v>4.137977326160445</v>
+        <v>4.142897986499258</v>
       </c>
       <c r="E33">
-        <v>0.05784213781291059</v>
+        <v>0.1048299329170714</v>
       </c>
       <c r="F33">
-        <v>1.456621648228982</v>
+        <v>1.503609443333143</v>
       </c>
       <c r="G33">
         <v>0.609</v>
@@ -4100,28 +4100,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M33">
-        <v>0.08419273126763517</v>
+        <v>0.08690862582465567</v>
       </c>
       <c r="N33">
-        <v>0.269807268732365</v>
+        <v>0.2670913741753445</v>
       </c>
       <c r="O33">
-        <v>0.08094218061970949</v>
+        <v>0.08012741225260334</v>
       </c>
       <c r="P33">
-        <v>0.1888650881126555</v>
+        <v>0.1869639619227411</v>
       </c>
       <c r="Q33">
-        <v>0.6048650881126555</v>
+        <v>0.6029639619227412</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08858705901816495</v>
+        <v>0.08907267645951517</v>
       </c>
       <c r="T33">
-        <v>0.9881537879483824</v>
+        <v>0.9993689713513895</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.204638508218613</v>
+        <v>4.073243554836781</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4146,22 +4146,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07351661999247031</v>
+        <v>0.0741740692624068</v>
       </c>
       <c r="C34">
-        <v>3.248288543166115</v>
+        <v>3.179968485053286</v>
       </c>
       <c r="D34">
-        <v>4.142897986499258</v>
+        <v>4.12156572349059</v>
       </c>
       <c r="E34">
-        <v>0.1048299329170714</v>
+        <v>0.1518177280212323</v>
       </c>
       <c r="F34">
-        <v>1.503609443333143</v>
+        <v>1.550597238437304</v>
       </c>
       <c r="G34">
         <v>0.609</v>
@@ -4182,45 +4182,45 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M34">
-        <v>0.08690862582465567</v>
+        <v>0.09505161071620671</v>
       </c>
       <c r="N34">
-        <v>0.2670913741753445</v>
+        <v>0.2589483892837934</v>
       </c>
       <c r="O34">
-        <v>0.08012741225260334</v>
+        <v>0.07768451678513803</v>
       </c>
       <c r="P34">
-        <v>0.1869639619227411</v>
+        <v>0.1812638724986554</v>
       </c>
       <c r="Q34">
-        <v>0.6029639619227412</v>
+        <v>0.5972638724986554</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08907267645951517</v>
+        <v>0.08957278994389076</v>
       </c>
       <c r="T34">
-        <v>0.9993689713513895</v>
+        <v>1.010918936348516</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.073243554836781</v>
+        <v>3.724292490496866</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4228,22 +4228,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0741740692624068</v>
+        <v>0.07404751853234329</v>
       </c>
       <c r="C35">
-        <v>3.179968485053286</v>
+        <v>3.137069792357825</v>
       </c>
       <c r="D35">
-        <v>4.12156572349059</v>
+        <v>4.125654825899289</v>
       </c>
       <c r="E35">
-        <v>0.1518177280212323</v>
+        <v>0.1988055231253929</v>
       </c>
       <c r="F35">
-        <v>1.550597238437304</v>
+        <v>1.597585033541464</v>
       </c>
       <c r="G35">
         <v>0.609</v>
@@ -4264,28 +4264,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M35">
-        <v>0.09505161071620671</v>
+        <v>0.09793196255609177</v>
       </c>
       <c r="N35">
-        <v>0.2589483892837934</v>
+        <v>0.2560680374439084</v>
       </c>
       <c r="O35">
-        <v>0.07768451678513803</v>
+        <v>0.07682041123317251</v>
       </c>
       <c r="P35">
-        <v>0.1812638724986554</v>
+        <v>0.1792476262107359</v>
       </c>
       <c r="Q35">
-        <v>0.5972638724986554</v>
+        <v>0.5952476262107358</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08957278994389076</v>
+        <v>0.09008805838233833</v>
       </c>
       <c r="T35">
-        <v>1.010918936348516</v>
+        <v>1.02281890028495</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.724292490496866</v>
+        <v>3.614754476070488</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4310,22 +4310,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07404751853234329</v>
+        <v>0.07392096780227977</v>
       </c>
       <c r="C36">
-        <v>3.137069792357825</v>
+        <v>3.094179221509819</v>
       </c>
       <c r="D36">
-        <v>4.125654825899289</v>
+        <v>4.129752050155444</v>
       </c>
       <c r="E36">
-        <v>0.1988055231253929</v>
+        <v>0.2457933182295537</v>
       </c>
       <c r="F36">
-        <v>1.597585033541464</v>
+        <v>1.644572828645625</v>
       </c>
       <c r="G36">
         <v>0.609</v>
@@ -4346,28 +4346,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M36">
-        <v>0.09793196255609177</v>
+        <v>0.1008123143959768</v>
       </c>
       <c r="N36">
-        <v>0.2560680374439084</v>
+        <v>0.2531876856040233</v>
       </c>
       <c r="O36">
-        <v>0.07682041123317251</v>
+        <v>0.075956305681207</v>
       </c>
       <c r="P36">
-        <v>0.1792476262107359</v>
+        <v>0.1772313799228163</v>
       </c>
       <c r="Q36">
-        <v>0.5952476262107358</v>
+        <v>0.5932313799228164</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09008805838233833</v>
+        <v>0.09061918123427659</v>
       </c>
       <c r="T36">
-        <v>1.02281890028495</v>
+        <v>1.035085016957889</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.614754476070488</v>
+        <v>3.511475776754188</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4392,22 +4392,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07392096780227977</v>
+        <v>0.07450001707221628</v>
       </c>
       <c r="C37">
-        <v>3.094179221509819</v>
+        <v>3.028510316315696</v>
       </c>
       <c r="D37">
-        <v>4.129752050155444</v>
+        <v>4.111070940065482</v>
       </c>
       <c r="E37">
-        <v>0.2457933182295537</v>
+        <v>0.2927811133337144</v>
       </c>
       <c r="F37">
-        <v>1.644572828645625</v>
+        <v>1.691560623749786</v>
       </c>
       <c r="G37">
         <v>0.609</v>
@@ -4428,45 +4428,45 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M37">
-        <v>0.1008123143959768</v>
+        <v>0.1084290359823613</v>
       </c>
       <c r="N37">
-        <v>0.2531876856040233</v>
+        <v>0.2455709640176389</v>
       </c>
       <c r="O37">
-        <v>0.075956305681207</v>
+        <v>0.07367128920529166</v>
       </c>
       <c r="P37">
-        <v>0.1772313799228163</v>
+        <v>0.1718996748123472</v>
       </c>
       <c r="Q37">
-        <v>0.5932313799228164</v>
+        <v>0.5878996748123473</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09061918123427659</v>
+        <v>0.09116690167533795</v>
       </c>
       <c r="T37">
-        <v>1.035085016957889</v>
+        <v>1.047734449776858</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.511475776754188</v>
+        <v>3.264808146570511</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4474,22 +4474,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07450001707221629</v>
+        <v>0.07439306634215276</v>
       </c>
       <c r="C38">
-        <v>3.028510316315696</v>
+        <v>2.984960196984944</v>
       </c>
       <c r="D38">
-        <v>4.111070940065481</v>
+        <v>4.11450861583889</v>
       </c>
       <c r="E38">
-        <v>0.2927811133337141</v>
+        <v>0.339768908437875</v>
       </c>
       <c r="F38">
-        <v>1.691560623749786</v>
+        <v>1.738548418853946</v>
       </c>
       <c r="G38">
         <v>0.609</v>
@@ -4510,28 +4510,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M38">
-        <v>0.1084290359823613</v>
+        <v>0.111440953648538</v>
       </c>
       <c r="N38">
-        <v>0.2455709640176389</v>
+        <v>0.2425590463514622</v>
       </c>
       <c r="O38">
-        <v>0.07367128920529166</v>
+        <v>0.07276771390543865</v>
       </c>
       <c r="P38">
-        <v>0.1718996748123472</v>
+        <v>0.1697913324460235</v>
       </c>
       <c r="Q38">
-        <v>0.5878996748123473</v>
+        <v>0.5857913324460235</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09116690167533795</v>
+        <v>0.09173201006690915</v>
       </c>
       <c r="T38">
-        <v>1.047734449776858</v>
+        <v>1.060785451891667</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.264808146570512</v>
+        <v>3.176570088555092</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4556,22 +4556,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07439306634215276</v>
+        <v>0.07428611561208925</v>
       </c>
       <c r="C39">
-        <v>2.984960196984944</v>
+        <v>2.941415831631707</v>
       </c>
       <c r="D39">
-        <v>4.11450861583889</v>
+        <v>4.117952045589814</v>
       </c>
       <c r="E39">
-        <v>0.339768908437875</v>
+        <v>0.3867567035420356</v>
       </c>
       <c r="F39">
-        <v>1.738548418853946</v>
+        <v>1.785536213958107</v>
       </c>
       <c r="G39">
         <v>0.609</v>
@@ -4592,28 +4592,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M39">
-        <v>0.111440953648538</v>
+        <v>0.1144528713147147</v>
       </c>
       <c r="N39">
-        <v>0.2425590463514622</v>
+        <v>0.2395471286852855</v>
       </c>
       <c r="O39">
-        <v>0.07276771390543865</v>
+        <v>0.07186413860558565</v>
       </c>
       <c r="P39">
-        <v>0.1697913324460235</v>
+        <v>0.1676829900796998</v>
       </c>
       <c r="Q39">
-        <v>0.5857913324460235</v>
+        <v>0.5836829900796998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09173201006690915</v>
+        <v>0.0923153477614343</v>
       </c>
       <c r="T39">
-        <v>1.060785451891667</v>
+        <v>1.074257454074695</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.176570088555092</v>
+        <v>3.092976138856274</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4638,22 +4638,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07428611561208925</v>
+        <v>0.07417916488202575</v>
       </c>
       <c r="C40">
-        <v>2.941415831631707</v>
+        <v>2.897877234714587</v>
       </c>
       <c r="D40">
-        <v>4.117952045589814</v>
+        <v>4.121401243776854</v>
       </c>
       <c r="E40">
-        <v>0.3867567035420356</v>
+        <v>0.4337444986461965</v>
       </c>
       <c r="F40">
-        <v>1.785536213958107</v>
+        <v>1.832524009062268</v>
       </c>
       <c r="G40">
         <v>0.609</v>
@@ -4674,28 +4674,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M40">
-        <v>0.1144528713147147</v>
+        <v>0.1174647889808914</v>
       </c>
       <c r="N40">
-        <v>0.2395471286852855</v>
+        <v>0.2365352110191088</v>
       </c>
       <c r="O40">
-        <v>0.07186413860558565</v>
+        <v>0.07096056330573262</v>
       </c>
       <c r="P40">
-        <v>0.1676829900796998</v>
+        <v>0.1655746477133762</v>
       </c>
       <c r="Q40">
-        <v>0.5836829900796998</v>
+        <v>0.5815746477133761</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0923153477614343</v>
+        <v>0.09291781128200943</v>
       </c>
       <c r="T40">
-        <v>1.074257454074695</v>
+        <v>1.088171161247331</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.092976138856274</v>
+        <v>3.013669058372779</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4720,22 +4720,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07417916488202575</v>
+        <v>0.07625621415196225</v>
       </c>
       <c r="C41">
-        <v>2.897877234714587</v>
+        <v>2.784920864334981</v>
       </c>
       <c r="D41">
-        <v>4.121401243776854</v>
+        <v>4.055432668501409</v>
       </c>
       <c r="E41">
-        <v>0.4337444986461965</v>
+        <v>0.4807322937503571</v>
       </c>
       <c r="F41">
-        <v>1.832524009062268</v>
+        <v>1.879511804166428</v>
       </c>
       <c r="G41">
         <v>0.609</v>
@@ -4756,45 +4756,45 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M41">
-        <v>0.1174647889808914</v>
+        <v>0.1351368987195662</v>
       </c>
       <c r="N41">
-        <v>0.2365352110191088</v>
+        <v>0.2188631012804339</v>
       </c>
       <c r="O41">
-        <v>0.07096056330573262</v>
+        <v>0.06565893038413018</v>
       </c>
       <c r="P41">
-        <v>0.1655746477133762</v>
+        <v>0.1532041708963038</v>
       </c>
       <c r="Q41">
-        <v>0.5815746477133761</v>
+        <v>0.5692041708963037</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09291781128200943</v>
+        <v>0.09354035691993708</v>
       </c>
       <c r="T41">
-        <v>1.088171161247331</v>
+        <v>1.102548658659055</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.013669058372779</v>
+        <v>2.619565813291416</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4802,22 +4802,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07625621415196225</v>
+        <v>0.07620386342189875</v>
       </c>
       <c r="C42">
-        <v>2.784920864334981</v>
+        <v>2.739569812595214</v>
       </c>
       <c r="D42">
-        <v>4.055432668501409</v>
+        <v>4.057069411865803</v>
       </c>
       <c r="E42">
-        <v>0.4807322937503571</v>
+        <v>0.5277200888545179</v>
       </c>
       <c r="F42">
-        <v>1.879511804166428</v>
+        <v>1.926499599270589</v>
       </c>
       <c r="G42">
         <v>0.609</v>
@@ -4838,28 +4838,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M42">
-        <v>0.1351368987195662</v>
+        <v>0.1385153211875554</v>
       </c>
       <c r="N42">
-        <v>0.2188631012804339</v>
+        <v>0.2154846788124448</v>
       </c>
       <c r="O42">
-        <v>0.06565893038413018</v>
+        <v>0.06464540364373343</v>
       </c>
       <c r="P42">
-        <v>0.1532041708963038</v>
+        <v>0.1508392751687113</v>
       </c>
       <c r="Q42">
-        <v>0.5692041708963037</v>
+        <v>0.5668392751687112</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09354035691993708</v>
+        <v>0.09418400579982837</v>
       </c>
       <c r="T42">
-        <v>1.102548658659055</v>
+        <v>1.117413528864397</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.619565813291416</v>
+        <v>2.555673964186747</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4884,22 +4884,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07620386342189875</v>
+        <v>0.07729811269183523</v>
       </c>
       <c r="C43">
-        <v>2.739569812595214</v>
+        <v>2.658642863634001</v>
       </c>
       <c r="D43">
-        <v>4.057069411865803</v>
+        <v>4.023130258008751</v>
       </c>
       <c r="E43">
-        <v>0.5277200888545179</v>
+        <v>0.5747078839586788</v>
       </c>
       <c r="F43">
-        <v>1.926499599270589</v>
+        <v>1.97348739437475</v>
       </c>
       <c r="G43">
         <v>0.609</v>
@@ -4920,45 +4920,45 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M43">
-        <v>0.1385153211875554</v>
+        <v>0.1495903444936061</v>
       </c>
       <c r="N43">
-        <v>0.2154846788124448</v>
+        <v>0.2044096555063941</v>
       </c>
       <c r="O43">
-        <v>0.06464540364373343</v>
+        <v>0.06132289665191822</v>
       </c>
       <c r="P43">
-        <v>0.1508392751687113</v>
+        <v>0.1430867588544759</v>
       </c>
       <c r="Q43">
-        <v>0.5668392751687112</v>
+        <v>0.5590867588544759</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09418400579982837</v>
+        <v>0.09484984946868144</v>
       </c>
       <c r="T43">
-        <v>1.117413528864397</v>
+        <v>1.132790980800957</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.555673964186747</v>
+        <v>2.366462897043005</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4966,22 +4966,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07729811269183523</v>
+        <v>0.07727306196177174</v>
       </c>
       <c r="C44">
-        <v>2.658642863634002</v>
+        <v>2.61242568798359</v>
       </c>
       <c r="D44">
-        <v>4.023130258008751</v>
+        <v>4.0239008774625</v>
       </c>
       <c r="E44">
-        <v>0.5747078839586783</v>
+        <v>0.6216956790628392</v>
       </c>
       <c r="F44">
-        <v>1.97348739437475</v>
+        <v>2.020475189478911</v>
       </c>
       <c r="G44">
         <v>0.609</v>
@@ -5002,28 +5002,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M44">
-        <v>0.149590344493606</v>
+        <v>0.1531520193625014</v>
       </c>
       <c r="N44">
-        <v>0.2044096555063941</v>
+        <v>0.2008479806374987</v>
       </c>
       <c r="O44">
-        <v>0.06132289665191823</v>
+        <v>0.06025439419124961</v>
       </c>
       <c r="P44">
-        <v>0.1430867588544759</v>
+        <v>0.1405935864462491</v>
       </c>
       <c r="Q44">
-        <v>0.5590867588544759</v>
+        <v>0.556593586446249</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09484984946868141</v>
+        <v>0.09553905607328372</v>
       </c>
       <c r="T44">
-        <v>1.132790980800957</v>
+        <v>1.14870799245459</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.366462897043005</v>
+        <v>2.31142887618154</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5048,22 +5048,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07727306196177174</v>
+        <v>0.07724801123170821</v>
       </c>
       <c r="C45">
-        <v>2.61242568798359</v>
+        <v>2.56620880760978</v>
       </c>
       <c r="D45">
-        <v>4.0239008774625</v>
+        <v>4.024671792192851</v>
       </c>
       <c r="E45">
-        <v>0.6216956790628392</v>
+        <v>0.668683474167</v>
       </c>
       <c r="F45">
-        <v>2.020475189478911</v>
+        <v>2.067462984583071</v>
       </c>
       <c r="G45">
         <v>0.609</v>
@@ -5084,28 +5084,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M45">
-        <v>0.1531520193625014</v>
+        <v>0.1567136942313968</v>
       </c>
       <c r="N45">
-        <v>0.2008479806374987</v>
+        <v>0.1972863057686033</v>
       </c>
       <c r="O45">
-        <v>0.06025439419124961</v>
+        <v>0.05918589173058099</v>
       </c>
       <c r="P45">
-        <v>0.1405935864462491</v>
+        <v>0.1381004140380223</v>
       </c>
       <c r="Q45">
-        <v>0.556593586446249</v>
+        <v>0.5541004140380223</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09553905607328372</v>
+        <v>0.09625287719947895</v>
       </c>
       <c r="T45">
-        <v>1.14870799245459</v>
+        <v>1.165193468810138</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.31142887618154</v>
+        <v>2.258896401722868</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5130,22 +5130,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07724801123170821</v>
+        <v>0.07722296050164471</v>
       </c>
       <c r="C46">
-        <v>2.56620880760978</v>
+        <v>2.519992222682315</v>
       </c>
       <c r="D46">
-        <v>4.024671792192851</v>
+        <v>4.025443002369547</v>
       </c>
       <c r="E46">
-        <v>0.668683474167</v>
+        <v>0.7156712692711609</v>
       </c>
       <c r="F46">
-        <v>2.067462984583071</v>
+        <v>2.114450779687232</v>
       </c>
       <c r="G46">
         <v>0.609</v>
@@ -5166,28 +5166,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M46">
-        <v>0.1567136942313968</v>
+        <v>0.1602753691002922</v>
       </c>
       <c r="N46">
-        <v>0.1972863057686033</v>
+        <v>0.1937246308997079</v>
       </c>
       <c r="O46">
-        <v>0.05918589173058099</v>
+        <v>0.05811738926991238</v>
       </c>
       <c r="P46">
-        <v>0.1381004140380223</v>
+        <v>0.1356072416297955</v>
       </c>
       <c r="Q46">
-        <v>0.5541004140380223</v>
+        <v>0.5516072416297955</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09625287719947895</v>
+        <v>0.09699265545753583</v>
       </c>
       <c r="T46">
-        <v>1.165193468810138</v>
+        <v>1.18227841703316</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.258896401722868</v>
+        <v>2.208698703906805</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5212,22 +5212,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07722296050164471</v>
+        <v>0.0771979097715812</v>
       </c>
       <c r="C47">
-        <v>2.519992222682315</v>
+        <v>2.47377593337107</v>
       </c>
       <c r="D47">
-        <v>4.025443002369547</v>
+        <v>4.026214508162463</v>
       </c>
       <c r="E47">
-        <v>0.7156712692711609</v>
+        <v>0.7626590643753213</v>
       </c>
       <c r="F47">
-        <v>2.114450779687232</v>
+        <v>2.161438574791393</v>
       </c>
       <c r="G47">
         <v>0.609</v>
@@ -5248,28 +5248,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M47">
-        <v>0.1602753691002922</v>
+        <v>0.1638370439691876</v>
       </c>
       <c r="N47">
-        <v>0.1937246308997079</v>
+        <v>0.1901629560308126</v>
       </c>
       <c r="O47">
-        <v>0.05811738926991238</v>
+        <v>0.05704888680924377</v>
       </c>
       <c r="P47">
-        <v>0.1356072416297955</v>
+        <v>0.1331140692215688</v>
       </c>
       <c r="Q47">
-        <v>0.5516072416297955</v>
+        <v>0.5491140692215688</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09699265545753583</v>
+        <v>0.09775983291033555</v>
       </c>
       <c r="T47">
-        <v>1.18227841703316</v>
+        <v>1.199996141116295</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.208698703906805</v>
+        <v>2.160683514691439</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5294,22 +5294,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0771979097715812</v>
+        <v>0.0771728590415177</v>
       </c>
       <c r="C48">
-        <v>2.47377593337107</v>
+        <v>2.427559939846046</v>
       </c>
       <c r="D48">
-        <v>4.026214508162463</v>
+        <v>4.026986309741599</v>
       </c>
       <c r="E48">
-        <v>0.7626590643753213</v>
+        <v>0.8096468594794821</v>
       </c>
       <c r="F48">
-        <v>2.161438574791393</v>
+        <v>2.208426369895554</v>
       </c>
       <c r="G48">
         <v>0.609</v>
@@ -5330,28 +5330,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M48">
-        <v>0.1638370439691876</v>
+        <v>0.167398718838083</v>
       </c>
       <c r="N48">
-        <v>0.1901629560308126</v>
+        <v>0.1866012811619172</v>
       </c>
       <c r="O48">
-        <v>0.05704888680924377</v>
+        <v>0.05598038434857516</v>
       </c>
       <c r="P48">
-        <v>0.1331140692215688</v>
+        <v>0.130620896813342</v>
       </c>
       <c r="Q48">
-        <v>0.5491140692215688</v>
+        <v>0.546620896813342</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09775983291033555</v>
+        <v>0.09855596045569376</v>
       </c>
       <c r="T48">
-        <v>1.199996141116295</v>
+        <v>1.218382458561057</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.160683514691439</v>
+        <v>2.114711525017154</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5376,22 +5376,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0771728590415177</v>
+        <v>0.07714780831145419</v>
       </c>
       <c r="C49">
-        <v>2.427559939846046</v>
+        <v>2.381344242277377</v>
       </c>
       <c r="D49">
-        <v>4.026986309741599</v>
+        <v>4.027758407277092</v>
       </c>
       <c r="E49">
-        <v>0.8096468594794821</v>
+        <v>0.856634654583643</v>
       </c>
       <c r="F49">
-        <v>2.208426369895554</v>
+        <v>2.255414164999714</v>
       </c>
       <c r="G49">
         <v>0.609</v>
@@ -5412,28 +5412,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M49">
-        <v>0.167398718838083</v>
+        <v>0.1709603937069784</v>
       </c>
       <c r="N49">
-        <v>0.1866012811619172</v>
+        <v>0.1830396062930218</v>
       </c>
       <c r="O49">
-        <v>0.05598038434857516</v>
+        <v>0.05491188188790654</v>
       </c>
       <c r="P49">
-        <v>0.130620896813342</v>
+        <v>0.1281277244051153</v>
       </c>
       <c r="Q49">
-        <v>0.546620896813342</v>
+        <v>0.5441277244051153</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09855596045569376</v>
+        <v>0.09938270829125805</v>
       </c>
       <c r="T49">
-        <v>1.218382458561057</v>
+        <v>1.237475942061387</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.114711525017154</v>
+        <v>2.07065503491263</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5458,22 +5458,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07714780831145418</v>
+        <v>0.07712275758139069</v>
       </c>
       <c r="C50">
-        <v>2.381344242277379</v>
+        <v>2.335128840835331</v>
       </c>
       <c r="D50">
-        <v>4.027758407277092</v>
+        <v>4.028530800939206</v>
       </c>
       <c r="E50">
-        <v>0.8566346545836425</v>
+        <v>0.9036224496878034</v>
       </c>
       <c r="F50">
-        <v>2.255414164999714</v>
+        <v>2.302401960103875</v>
       </c>
       <c r="G50">
         <v>0.609</v>
@@ -5494,28 +5494,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M50">
-        <v>0.1709603937069783</v>
+        <v>0.1745220685758737</v>
       </c>
       <c r="N50">
-        <v>0.1830396062930218</v>
+        <v>0.1794779314241264</v>
       </c>
       <c r="O50">
-        <v>0.05491188188790654</v>
+        <v>0.05384337942723793</v>
       </c>
       <c r="P50">
-        <v>0.1281277244051153</v>
+        <v>0.1256345519968885</v>
       </c>
       <c r="Q50">
-        <v>0.5441277244051153</v>
+        <v>0.5416345519968885</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09938270829125805</v>
+        <v>0.10024187761057</v>
       </c>
       <c r="T50">
-        <v>1.237475942061387</v>
+        <v>1.257318189620553</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.07065503491263</v>
+        <v>2.028396768894005</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5540,22 +5540,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07712275758139069</v>
+        <v>0.08206770685132717</v>
       </c>
       <c r="C51">
-        <v>2.335128840835331</v>
+        <v>2.141205460878451</v>
       </c>
       <c r="D51">
-        <v>4.028530800939206</v>
+        <v>3.881595216086486</v>
       </c>
       <c r="E51">
-        <v>0.9036224496878034</v>
+        <v>0.9506102447919642</v>
       </c>
       <c r="F51">
-        <v>2.302401960103875</v>
+        <v>2.349389755208036</v>
       </c>
       <c r="G51">
         <v>0.609</v>
@@ -5576,45 +5576,45 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M51">
-        <v>0.1745220685758737</v>
+        <v>0.2114450779687232</v>
       </c>
       <c r="N51">
-        <v>0.1794779314241264</v>
+        <v>0.142554922031277</v>
       </c>
       <c r="O51">
-        <v>0.05384337942723793</v>
+        <v>0.04276647660938308</v>
       </c>
       <c r="P51">
-        <v>0.1256345519968885</v>
+        <v>0.09978844542189387</v>
       </c>
       <c r="Q51">
-        <v>0.5416345519968885</v>
+        <v>0.5157884454218938</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.10024187761057</v>
+        <v>0.1011354137026543</v>
       </c>
       <c r="T51">
-        <v>1.257318189620553</v>
+        <v>1.277954127082087</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.028396768894005</v>
+        <v>1.674193617561358</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5622,22 +5622,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08206770685132717</v>
+        <v>0.08214205612126367</v>
       </c>
       <c r="C52">
-        <v>2.141205460878451</v>
+        <v>2.092090176845841</v>
       </c>
       <c r="D52">
-        <v>3.881595216086486</v>
+        <v>3.879467727158038</v>
       </c>
       <c r="E52">
-        <v>0.9506102447919642</v>
+        <v>0.9975980398961251</v>
       </c>
       <c r="F52">
-        <v>2.349389755208036</v>
+        <v>2.396377550312196</v>
       </c>
       <c r="G52">
         <v>0.609</v>
@@ -5658,28 +5658,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M52">
-        <v>0.2114450779687232</v>
+        <v>0.2156739795280977</v>
       </c>
       <c r="N52">
-        <v>0.142554922031277</v>
+        <v>0.1383260204719025</v>
       </c>
       <c r="O52">
-        <v>0.04276647660938308</v>
+        <v>0.04149780614157075</v>
       </c>
       <c r="P52">
-        <v>0.09978844542189387</v>
+        <v>0.09682821433033173</v>
       </c>
       <c r="Q52">
-        <v>0.5157884454218938</v>
+        <v>0.5128282143303318</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1011354137026543</v>
+        <v>0.1020654206556401</v>
       </c>
       <c r="T52">
-        <v>1.277954127082087</v>
+        <v>1.299432347705315</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.674193617561358</v>
+        <v>1.641366291726822</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5704,22 +5704,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08214205612126367</v>
+        <v>0.08221640539120016</v>
       </c>
       <c r="C53">
-        <v>2.092090176845841</v>
+        <v>2.042977223674359</v>
       </c>
       <c r="D53">
-        <v>3.879467727158038</v>
+        <v>3.877342569090717</v>
       </c>
       <c r="E53">
-        <v>0.9975980398961251</v>
+        <v>1.044585835000286</v>
       </c>
       <c r="F53">
-        <v>2.396377550312196</v>
+        <v>2.443365345416357</v>
       </c>
       <c r="G53">
         <v>0.609</v>
@@ -5740,28 +5740,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M53">
-        <v>0.2156739795280977</v>
+        <v>0.2199028810874722</v>
       </c>
       <c r="N53">
-        <v>0.1383260204719025</v>
+        <v>0.134097118912528</v>
       </c>
       <c r="O53">
-        <v>0.04149780614157075</v>
+        <v>0.0402291356737584</v>
       </c>
       <c r="P53">
-        <v>0.09682821433033173</v>
+        <v>0.09386798323876959</v>
       </c>
       <c r="Q53">
-        <v>0.5128282143303318</v>
+        <v>0.5098679832387696</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1020654206556401</v>
+        <v>0.1030341778983337</v>
       </c>
       <c r="T53">
-        <v>1.299432347705315</v>
+        <v>1.321805494187845</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.641366291726822</v>
+        <v>1.60980155534746</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5786,22 +5786,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08221640539120016</v>
+        <v>0.08229075466113664</v>
       </c>
       <c r="C54">
-        <v>2.042977223674359</v>
+        <v>1.993866597535591</v>
       </c>
       <c r="D54">
-        <v>3.877342569090717</v>
+        <v>3.875219738056109</v>
       </c>
       <c r="E54">
-        <v>1.044585835000286</v>
+        <v>1.091573630104446</v>
       </c>
       <c r="F54">
-        <v>2.443365345416357</v>
+        <v>2.490353140520518</v>
       </c>
       <c r="G54">
         <v>0.609</v>
@@ -5822,28 +5822,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M54">
-        <v>0.2199028810874722</v>
+        <v>0.2241317826468466</v>
       </c>
       <c r="N54">
-        <v>0.134097118912528</v>
+        <v>0.1298682173531536</v>
       </c>
       <c r="O54">
-        <v>0.0402291356737584</v>
+        <v>0.03896046520594607</v>
       </c>
       <c r="P54">
-        <v>0.09386798323876959</v>
+        <v>0.0909077521472075</v>
       </c>
       <c r="Q54">
-        <v>0.5098679832387696</v>
+        <v>0.5069077521472075</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1030341778983337</v>
+        <v>0.1040441588534822</v>
       </c>
       <c r="T54">
-        <v>1.321805494187845</v>
+        <v>1.345130689456865</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.60980155534746</v>
+        <v>1.579427941095621</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5868,22 +5868,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08229075466113664</v>
+        <v>0.08236510393107313</v>
       </c>
       <c r="C55">
-        <v>1.993866597535591</v>
+        <v>1.944758294609501</v>
       </c>
       <c r="D55">
-        <v>3.875219738056109</v>
+        <v>3.873099230234179</v>
       </c>
       <c r="E55">
-        <v>1.091573630104446</v>
+        <v>1.138561425208607</v>
       </c>
       <c r="F55">
-        <v>2.490353140520518</v>
+        <v>2.537340935624679</v>
       </c>
       <c r="G55">
         <v>0.609</v>
@@ -5904,28 +5904,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M55">
-        <v>0.2241317826468466</v>
+        <v>0.228360684206221</v>
       </c>
       <c r="N55">
-        <v>0.1298682173531536</v>
+        <v>0.1256393157937791</v>
       </c>
       <c r="O55">
-        <v>0.03896046520594607</v>
+        <v>0.03769179473813373</v>
       </c>
       <c r="P55">
-        <v>0.0909077521472075</v>
+        <v>0.08794752105564538</v>
       </c>
       <c r="Q55">
-        <v>0.5069077521472075</v>
+        <v>0.5039475210556453</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1040441588534822</v>
+        <v>0.105098052024072</v>
       </c>
       <c r="T55">
-        <v>1.345130689456865</v>
+        <v>1.369470023650625</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.579427941095621</v>
+        <v>1.550179275519776</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5950,22 +5950,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08236510393107313</v>
+        <v>0.08243945320100962</v>
       </c>
       <c r="C56">
-        <v>1.944758294609501</v>
+        <v>1.895652311084411</v>
       </c>
       <c r="D56">
-        <v>3.873099230234179</v>
+        <v>3.87098104181325</v>
       </c>
       <c r="E56">
-        <v>1.138561425208607</v>
+        <v>1.185549220312768</v>
       </c>
       <c r="F56">
-        <v>2.537340935624679</v>
+        <v>2.584328730728839</v>
       </c>
       <c r="G56">
         <v>0.609</v>
@@ -5986,28 +5986,28 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M56">
-        <v>0.228360684206221</v>
+        <v>0.2325895857655955</v>
       </c>
       <c r="N56">
-        <v>0.1256393157937791</v>
+        <v>0.1214104142344046</v>
       </c>
       <c r="O56">
-        <v>0.03769179473813373</v>
+        <v>0.03642312427032138</v>
       </c>
       <c r="P56">
-        <v>0.08794752105564538</v>
+        <v>0.08498728996408322</v>
       </c>
       <c r="Q56">
-        <v>0.5039475210556453</v>
+        <v>0.5009872899640833</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.105098052024072</v>
+        <v>0.1061987848911325</v>
       </c>
       <c r="T56">
-        <v>1.369470023650625</v>
+        <v>1.394891106030774</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.550179275519776</v>
+        <v>1.521994197783053</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6032,22 +6032,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08243945320100962</v>
+        <v>0.1072971306713657</v>
       </c>
       <c r="C57">
-        <v>1.895652311084411</v>
+        <v>1.250277758788933</v>
       </c>
       <c r="D57">
-        <v>3.87098104181325</v>
+        <v>3.272594284621933</v>
       </c>
       <c r="E57">
-        <v>1.185549220312768</v>
+        <v>1.232537015416929</v>
       </c>
       <c r="F57">
-        <v>2.584328730728839</v>
+        <v>2.631316525833</v>
       </c>
       <c r="G57">
         <v>0.609</v>
@@ -6068,45 +6068,45 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M57">
-        <v>0.2325895857655955</v>
+        <v>0.3862772659922845</v>
       </c>
       <c r="N57">
-        <v>0.1214104142344046</v>
+        <v>-0.03227726599228431</v>
       </c>
       <c r="O57">
-        <v>0.03642312427032138</v>
+        <v>-0.009683179797685293</v>
       </c>
       <c r="P57">
-        <v>0.08498728996408322</v>
+        <v>-0.02259408619459902</v>
       </c>
       <c r="Q57">
-        <v>0.5009872899640833</v>
+        <v>0.393405913805401</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1061987848911325</v>
+        <v>0.1083880557010092</v>
       </c>
       <c r="T57">
-        <v>1.394891106030774</v>
+        <v>1.445451632817764</v>
       </c>
       <c r="U57">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.3</v>
+        <v>0.2749320484268968</v>
       </c>
       <c r="W57">
-        <v>0.063</v>
+        <v>0.1064399752909316</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.521994197783053</v>
+        <v>0.9164401614229893</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6114,22 +6114,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1072971306713657</v>
+        <v>0.1083071306713657</v>
       </c>
       <c r="C58">
-        <v>1.250277758788933</v>
+        <v>1.182863429122898</v>
       </c>
       <c r="D58">
-        <v>3.272594284621933</v>
+        <v>3.252167750060059</v>
       </c>
       <c r="E58">
-        <v>1.232537015416929</v>
+        <v>1.27952481052109</v>
       </c>
       <c r="F58">
-        <v>2.631316525833</v>
+        <v>2.678304320937161</v>
       </c>
       <c r="G58">
         <v>0.609</v>
@@ -6150,37 +6150,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M58">
-        <v>0.3862772659922845</v>
+        <v>0.3931750743135753</v>
       </c>
       <c r="N58">
-        <v>-0.03227726599228431</v>
+        <v>-0.03917507431357514</v>
       </c>
       <c r="O58">
-        <v>-0.009683179797685293</v>
+        <v>-0.01175252229407254</v>
       </c>
       <c r="P58">
-        <v>-0.02259408619459902</v>
+        <v>-0.0274225520195026</v>
       </c>
       <c r="Q58">
-        <v>0.393405913805401</v>
+        <v>0.3885774479804974</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1083880557010092</v>
+        <v>0.1098435918801024</v>
       </c>
       <c r="T58">
-        <v>1.445451632817764</v>
+        <v>1.47906678706934</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2749320484268968</v>
+        <v>0.2701086791562494</v>
       </c>
       <c r="W58">
-        <v>0.1064399752909316</v>
+        <v>0.1071480458998626</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9164401614229893</v>
+        <v>0.9003622638541648</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6196,22 +6196,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1083071306713657</v>
+        <v>0.1093171306713657</v>
       </c>
       <c r="C59">
-        <v>1.182863429122898</v>
+        <v>1.115702510131814</v>
       </c>
       <c r="D59">
-        <v>3.252167750060059</v>
+        <v>3.231994626173135</v>
       </c>
       <c r="E59">
-        <v>1.27952481052109</v>
+        <v>1.32651260562525</v>
       </c>
       <c r="F59">
-        <v>2.678304320937161</v>
+        <v>2.725292116041321</v>
       </c>
       <c r="G59">
         <v>0.609</v>
@@ -6232,37 +6232,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M59">
-        <v>0.3931750743135753</v>
+        <v>0.400072882634866</v>
       </c>
       <c r="N59">
-        <v>-0.03917507431357514</v>
+        <v>-0.04607288263486586</v>
       </c>
       <c r="O59">
-        <v>-0.01175252229407254</v>
+        <v>-0.01382186479045976</v>
       </c>
       <c r="P59">
-        <v>-0.0274225520195026</v>
+        <v>-0.03225101784440611</v>
       </c>
       <c r="Q59">
-        <v>0.3885774479804974</v>
+        <v>0.3837489821555939</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1098435918801024</v>
+        <v>0.1113684393058191</v>
       </c>
       <c r="T59">
-        <v>1.47906678706934</v>
+        <v>1.514282662951943</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2701086791562494</v>
+        <v>0.2654516329639003</v>
       </c>
       <c r="W59">
-        <v>0.1071480458998626</v>
+        <v>0.1078317002808994</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9003622638541648</v>
+        <v>0.8848387765463346</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6278,22 +6278,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1093171306713657</v>
+        <v>0.1103271306713657</v>
       </c>
       <c r="C60">
-        <v>1.115702510131815</v>
+        <v>1.048790315184486</v>
       </c>
       <c r="D60">
-        <v>3.231994626173136</v>
+        <v>3.212070226329968</v>
       </c>
       <c r="E60">
-        <v>1.32651260562525</v>
+        <v>1.37350040072941</v>
       </c>
       <c r="F60">
-        <v>2.725292116041321</v>
+        <v>2.772279911145482</v>
       </c>
       <c r="G60">
         <v>0.609</v>
@@ -6314,37 +6314,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M60">
-        <v>0.400072882634866</v>
+        <v>0.4069706909561568</v>
       </c>
       <c r="N60">
-        <v>-0.04607288263486581</v>
+        <v>-0.05297069095615664</v>
       </c>
       <c r="O60">
-        <v>-0.01382186479045974</v>
+        <v>-0.01589120728684699</v>
       </c>
       <c r="P60">
-        <v>-0.03225101784440607</v>
+        <v>-0.03707948366930965</v>
       </c>
       <c r="Q60">
-        <v>0.3837489821555939</v>
+        <v>0.3789205163306903</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1113684393058191</v>
+        <v>0.1129676695327903</v>
       </c>
       <c r="T60">
-        <v>1.514282662951943</v>
+        <v>1.551216386438575</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2654516329639004</v>
+        <v>0.2609524527441733</v>
       </c>
       <c r="W60">
-        <v>0.1078317002808994</v>
+        <v>0.1084921799371554</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8848387765463347</v>
+        <v>0.8698415091472442</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6360,22 +6360,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1103271306713657</v>
+        <v>0.1113371306713657</v>
       </c>
       <c r="C61">
-        <v>1.048790315184486</v>
+        <v>0.9821222725090522</v>
       </c>
       <c r="D61">
-        <v>3.212070226329968</v>
+        <v>3.192389978758695</v>
       </c>
       <c r="E61">
-        <v>1.37350040072941</v>
+        <v>1.420488195833571</v>
       </c>
       <c r="F61">
-        <v>2.772279911145482</v>
+        <v>2.819267706249643</v>
       </c>
       <c r="G61">
         <v>0.609</v>
@@ -6396,37 +6396,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M61">
-        <v>0.4069706909561568</v>
+        <v>0.4138684992774476</v>
       </c>
       <c r="N61">
-        <v>-0.05297069095615664</v>
+        <v>-0.05986849927744742</v>
       </c>
       <c r="O61">
-        <v>-0.01589120728684699</v>
+        <v>-0.01796054978323422</v>
       </c>
       <c r="P61">
-        <v>-0.03707948366930965</v>
+        <v>-0.0419079494942132</v>
       </c>
       <c r="Q61">
-        <v>0.3789205163306903</v>
+        <v>0.3740920505057868</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1129676695327903</v>
+        <v>0.1146468612711101</v>
       </c>
       <c r="T61">
-        <v>1.551216386438575</v>
+        <v>1.58999679609954</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2609524527441733</v>
+        <v>0.256603245198437</v>
       </c>
       <c r="W61">
-        <v>0.1084921799371554</v>
+        <v>0.1091306436048695</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8698415091472442</v>
+        <v>0.8553441506614569</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6442,22 +6442,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1113371306713657</v>
+        <v>0.1123471306713657</v>
       </c>
       <c r="C62">
-        <v>0.9821222725090522</v>
+        <v>0.9156939216957189</v>
       </c>
       <c r="D62">
-        <v>3.192389978758695</v>
+        <v>3.172949423049523</v>
       </c>
       <c r="E62">
-        <v>1.420488195833571</v>
+        <v>1.467475990937732</v>
       </c>
       <c r="F62">
-        <v>2.819267706249643</v>
+        <v>2.866255501353804</v>
       </c>
       <c r="G62">
         <v>0.609</v>
@@ -6478,37 +6478,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M62">
-        <v>0.4138684992774476</v>
+        <v>0.4207663075987384</v>
       </c>
       <c r="N62">
-        <v>-0.05986849927744742</v>
+        <v>-0.06676630759873825</v>
       </c>
       <c r="O62">
-        <v>-0.01796054978323422</v>
+        <v>-0.02002989227962148</v>
       </c>
       <c r="P62">
-        <v>-0.0419079494942132</v>
+        <v>-0.04673641531911678</v>
       </c>
       <c r="Q62">
-        <v>0.3740920505057868</v>
+        <v>0.3692635846808832</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1146468612711101</v>
+        <v>0.1164121654062667</v>
       </c>
       <c r="T62">
-        <v>1.58999679609954</v>
+        <v>1.630765944717477</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.256603245198437</v>
+        <v>0.2523966346214135</v>
       </c>
       <c r="W62">
-        <v>0.1091306436048695</v>
+        <v>0.1097481740375765</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8553441506614569</v>
+        <v>0.8413221154047116</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6524,22 +6524,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1123471306713657</v>
+        <v>0.1133571306713657</v>
       </c>
       <c r="C63">
-        <v>0.9156939216957189</v>
+        <v>0.8495009103264977</v>
       </c>
       <c r="D63">
-        <v>3.172949423049523</v>
+        <v>3.153744206784462</v>
       </c>
       <c r="E63">
-        <v>1.467475990937732</v>
+        <v>1.514463786041893</v>
       </c>
       <c r="F63">
-        <v>2.866255501353804</v>
+        <v>2.913243296457964</v>
       </c>
       <c r="G63">
         <v>0.609</v>
@@ -6560,37 +6560,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M63">
-        <v>0.4207663075987384</v>
+        <v>0.4276641159200292</v>
       </c>
       <c r="N63">
-        <v>-0.06676630759873825</v>
+        <v>-0.07366411592002903</v>
       </c>
       <c r="O63">
-        <v>-0.02002989227962148</v>
+        <v>-0.02209923477600871</v>
       </c>
       <c r="P63">
-        <v>-0.04673641531911678</v>
+        <v>-0.05156488114402032</v>
       </c>
       <c r="Q63">
-        <v>0.3692635846808832</v>
+        <v>0.3644351188559797</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1164121654062667</v>
+        <v>0.118270380285379</v>
       </c>
       <c r="T63">
-        <v>1.630765944717477</v>
+        <v>1.673680837999516</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2523966346214135</v>
+        <v>0.2483257211597778</v>
       </c>
       <c r="W63">
-        <v>0.1097481740375765</v>
+        <v>0.1103457841337446</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8413221154047116</v>
+        <v>0.8277524038659259</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6606,22 +6606,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1133571306713657</v>
+        <v>0.1143671306713657</v>
       </c>
       <c r="C64">
-        <v>0.8495009103264977</v>
+        <v>0.783538990726607</v>
       </c>
       <c r="D64">
-        <v>3.153744206784462</v>
+        <v>3.134770082288732</v>
       </c>
       <c r="E64">
-        <v>1.514463786041893</v>
+        <v>1.561451581146053</v>
       </c>
       <c r="F64">
-        <v>2.913243296457964</v>
+        <v>2.960231091562125</v>
       </c>
       <c r="G64">
         <v>0.609</v>
@@ -6642,37 +6642,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M64">
-        <v>0.4276641159200292</v>
+        <v>0.43456192424132</v>
       </c>
       <c r="N64">
-        <v>-0.07366411592002903</v>
+        <v>-0.0805619242413198</v>
       </c>
       <c r="O64">
-        <v>-0.02209923477600871</v>
+        <v>-0.02416857727239594</v>
       </c>
       <c r="P64">
-        <v>-0.05156488114402032</v>
+        <v>-0.05639334696892387</v>
       </c>
       <c r="Q64">
-        <v>0.3644351188559797</v>
+        <v>0.3596066530310761</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.118270380285379</v>
+        <v>0.1202290392120109</v>
       </c>
       <c r="T64">
-        <v>1.673680837999516</v>
+        <v>1.718915455242745</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2483257211597778</v>
+        <v>0.2443840430461305</v>
       </c>
       <c r="W64">
-        <v>0.1103457841337446</v>
+        <v>0.1109244224808281</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8277524038659259</v>
+        <v>0.8146134768204351</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6688,22 +6688,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1143671306713657</v>
+        <v>0.1153771306713657</v>
       </c>
       <c r="C65">
-        <v>0.783538990726607</v>
+        <v>0.71780401683244</v>
       </c>
       <c r="D65">
-        <v>3.134770082288732</v>
+        <v>3.116022903498726</v>
       </c>
       <c r="E65">
-        <v>1.561451581146053</v>
+        <v>1.608439376250214</v>
       </c>
       <c r="F65">
-        <v>2.960231091562125</v>
+        <v>3.007218886666286</v>
       </c>
       <c r="G65">
         <v>0.609</v>
@@ -6724,37 +6724,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M65">
-        <v>0.43456192424132</v>
+        <v>0.4414597325626108</v>
       </c>
       <c r="N65">
-        <v>-0.0805619242413198</v>
+        <v>-0.08745973256261064</v>
       </c>
       <c r="O65">
-        <v>-0.02416857727239594</v>
+        <v>-0.02623791976878319</v>
       </c>
       <c r="P65">
-        <v>-0.05639334696892387</v>
+        <v>-0.06122181279382745</v>
       </c>
       <c r="Q65">
-        <v>0.3596066530310761</v>
+        <v>0.3547781872061725</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1202290392120109</v>
+        <v>0.1222965125234556</v>
       </c>
       <c r="T65">
-        <v>1.718915455242745</v>
+        <v>1.766663106777267</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2443840430461305</v>
+        <v>0.2405655423735347</v>
       </c>
       <c r="W65">
-        <v>0.1109244224808281</v>
+        <v>0.1114849783795651</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8146134768204351</v>
+        <v>0.8018851412451157</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6770,22 +6770,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1153771306713657</v>
+        <v>0.1528348445044691</v>
       </c>
       <c r="C66">
-        <v>0.71780401683244</v>
+        <v>0.105159808820229</v>
       </c>
       <c r="D66">
-        <v>3.116022903498726</v>
+        <v>2.550366490590676</v>
       </c>
       <c r="E66">
-        <v>1.608439376250214</v>
+        <v>1.655427171354375</v>
       </c>
       <c r="F66">
-        <v>3.007218886666286</v>
+        <v>3.054206681770447</v>
       </c>
       <c r="G66">
         <v>0.609</v>
@@ -6806,45 +6806,45 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M66">
-        <v>0.4414597325626108</v>
+        <v>0.6132847016995057</v>
       </c>
       <c r="N66">
-        <v>-0.08745973256261064</v>
+        <v>-0.2592847016995055</v>
       </c>
       <c r="O66">
-        <v>-0.02623791976878319</v>
+        <v>-0.07778541050985165</v>
       </c>
       <c r="P66">
-        <v>-0.06122181279382745</v>
+        <v>-0.1814992911896539</v>
       </c>
       <c r="Q66">
-        <v>0.3547781872061725</v>
+        <v>0.2345007088103461</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1222965125234556</v>
+        <v>0.1283327381187069</v>
       </c>
       <c r="T66">
-        <v>1.766663106777267</v>
+        <v>1.906067854935495</v>
       </c>
       <c r="U66">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.2405655423735347</v>
+        <v>0.1731659043600853</v>
       </c>
       <c r="W66">
-        <v>0.1114849783795651</v>
+        <v>0.1660282864044949</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8018851412451157</v>
+        <v>0.5772196812002843</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6852,22 +6852,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1528348445044691</v>
+        <v>0.1543848445044691</v>
       </c>
       <c r="C67">
-        <v>0.105159808820229</v>
+        <v>0.03915707333011564</v>
       </c>
       <c r="D67">
-        <v>2.550366490590676</v>
+        <v>2.531351550204723</v>
       </c>
       <c r="E67">
-        <v>1.655427171354375</v>
+        <v>1.702414966458536</v>
       </c>
       <c r="F67">
-        <v>3.054206681770447</v>
+        <v>3.101194476874607</v>
       </c>
       <c r="G67">
         <v>0.609</v>
@@ -6888,37 +6888,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M67">
-        <v>0.6132847016995057</v>
+        <v>0.6227198509564211</v>
       </c>
       <c r="N67">
-        <v>-0.2592847016995055</v>
+        <v>-0.268719850956421</v>
       </c>
       <c r="O67">
-        <v>-0.07778541050985165</v>
+        <v>-0.08061595528692629</v>
       </c>
       <c r="P67">
-        <v>-0.1814992911896539</v>
+        <v>-0.1881038956694947</v>
       </c>
       <c r="Q67">
-        <v>0.2345007088103461</v>
+        <v>0.2278961043305053</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1283327381187069</v>
+        <v>0.1307601715927865</v>
       </c>
       <c r="T67">
-        <v>1.906067854935495</v>
+        <v>1.962128674198303</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1731659043600853</v>
+        <v>0.1705421785364476</v>
       </c>
       <c r="W67">
-        <v>0.1660282864044949</v>
+        <v>0.1665551305498813</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5772196812002843</v>
+        <v>0.5684739284548255</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6934,22 +6934,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1543848445044691</v>
+        <v>0.1559348445044691</v>
       </c>
       <c r="C68">
-        <v>0.03915707333011564</v>
+        <v>-0.02656421857710001</v>
       </c>
       <c r="D68">
-        <v>2.531351550204723</v>
+        <v>2.512618053401668</v>
       </c>
       <c r="E68">
-        <v>1.702414966458536</v>
+        <v>1.749402761562696</v>
       </c>
       <c r="F68">
-        <v>3.101194476874607</v>
+        <v>3.148182271978768</v>
       </c>
       <c r="G68">
         <v>0.609</v>
@@ -6970,37 +6970,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M68">
-        <v>0.6227198509564211</v>
+        <v>0.6321550002133366</v>
       </c>
       <c r="N68">
-        <v>-0.268719850956421</v>
+        <v>-0.2781550002133364</v>
       </c>
       <c r="O68">
-        <v>-0.08061595528692629</v>
+        <v>-0.08344650006400094</v>
       </c>
       <c r="P68">
-        <v>-0.1881038956694947</v>
+        <v>-0.1947085001493355</v>
       </c>
       <c r="Q68">
-        <v>0.2278961043305053</v>
+        <v>0.2212914998506645</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1307601715927865</v>
+        <v>0.1333347222471134</v>
       </c>
       <c r="T68">
-        <v>1.962128674198303</v>
+        <v>2.021587118870979</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1705421785364476</v>
+        <v>0.1679967728866499</v>
       </c>
       <c r="W68">
-        <v>0.1665551305498813</v>
+        <v>0.1670662480043607</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5684739284548255</v>
+        <v>0.5599892429554998</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7016,22 +7016,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1559348445044691</v>
+        <v>0.1574848445044691</v>
       </c>
       <c r="C69">
-        <v>-0.02656421857710001</v>
+        <v>-0.09201026954450331</v>
       </c>
       <c r="D69">
-        <v>2.512618053401668</v>
+        <v>2.494159797538425</v>
       </c>
       <c r="E69">
-        <v>1.749402761562696</v>
+        <v>1.796390556666857</v>
       </c>
       <c r="F69">
-        <v>3.148182271978768</v>
+        <v>3.195170067082929</v>
       </c>
       <c r="G69">
         <v>0.609</v>
@@ -7052,37 +7052,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M69">
-        <v>0.6321550002133366</v>
+        <v>0.6415901494702521</v>
       </c>
       <c r="N69">
-        <v>-0.2781550002133364</v>
+        <v>-0.2875901494702519</v>
       </c>
       <c r="O69">
-        <v>-0.08344650006400094</v>
+        <v>-0.08627704484107557</v>
       </c>
       <c r="P69">
-        <v>-0.1947085001493355</v>
+        <v>-0.2013131046291763</v>
       </c>
       <c r="Q69">
-        <v>0.2212914998506645</v>
+        <v>0.2146868953708236</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1333347222471134</v>
+        <v>0.1360701823173357</v>
       </c>
       <c r="T69">
-        <v>2.021587118870979</v>
+        <v>2.084761716335697</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1679967728866499</v>
+        <v>0.1655262321089051</v>
       </c>
       <c r="W69">
-        <v>0.1670662480043607</v>
+        <v>0.1675623325925319</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5599892429554998</v>
+        <v>0.5517541070296836</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7098,22 +7098,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1574848445044691</v>
+        <v>0.1590348445044691</v>
       </c>
       <c r="C70">
-        <v>-0.09201026954450331</v>
+        <v>-0.157187101280337</v>
       </c>
       <c r="D70">
-        <v>2.494159797538425</v>
+        <v>2.475970760906752</v>
       </c>
       <c r="E70">
-        <v>1.796390556666857</v>
+        <v>1.843378351771018</v>
       </c>
       <c r="F70">
-        <v>3.195170067082929</v>
+        <v>3.242157862187089</v>
       </c>
       <c r="G70">
         <v>0.609</v>
@@ -7134,37 +7134,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M70">
-        <v>0.6415901494702521</v>
+        <v>0.6510252987271676</v>
       </c>
       <c r="N70">
-        <v>-0.2875901494702519</v>
+        <v>-0.2970252987271675</v>
       </c>
       <c r="O70">
-        <v>-0.08627704484107557</v>
+        <v>-0.08910758961815024</v>
       </c>
       <c r="P70">
-        <v>-0.2013131046291763</v>
+        <v>-0.2079177091090172</v>
       </c>
       <c r="Q70">
-        <v>0.2146868953708236</v>
+        <v>0.2080822908909827</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1360701823173357</v>
+        <v>0.1389821236824111</v>
       </c>
       <c r="T70">
-        <v>2.084761716335697</v>
+        <v>2.152012094282011</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1655262321089051</v>
+        <v>0.163127301208776</v>
       </c>
       <c r="W70">
-        <v>0.1675623325925319</v>
+        <v>0.1680440379172778</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5517541070296836</v>
+        <v>0.54375767069592</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7180,22 +7180,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1590348445044691</v>
+        <v>0.1605848445044691</v>
       </c>
       <c r="C71">
-        <v>-0.157187101280337</v>
+        <v>-0.2221005611077085</v>
       </c>
       <c r="D71">
-        <v>2.475970760906752</v>
+        <v>2.458045096183542</v>
       </c>
       <c r="E71">
-        <v>1.843378351771018</v>
+        <v>1.890366146875179</v>
       </c>
       <c r="F71">
-        <v>3.242157862187089</v>
+        <v>3.28914565729125</v>
       </c>
       <c r="G71">
         <v>0.609</v>
@@ -7216,37 +7216,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M71">
-        <v>0.6510252987271676</v>
+        <v>0.6604604479840831</v>
       </c>
       <c r="N71">
-        <v>-0.2970252987271675</v>
+        <v>-0.306460447984083</v>
       </c>
       <c r="O71">
-        <v>-0.08910758961815024</v>
+        <v>-0.09193813439522489</v>
       </c>
       <c r="P71">
-        <v>-0.2079177091090172</v>
+        <v>-0.2145223135888581</v>
       </c>
       <c r="Q71">
-        <v>0.2080822908909827</v>
+        <v>0.2014776864111419</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1389821236824111</v>
+        <v>0.1420881944718247</v>
       </c>
       <c r="T71">
-        <v>2.152012094282011</v>
+        <v>2.223745830758078</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.163127301208776</v>
+        <v>0.1607969111915078</v>
       </c>
       <c r="W71">
-        <v>0.1680440379172778</v>
+        <v>0.1685119802327452</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.54375767069592</v>
+        <v>0.5359897039716925</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7262,22 +7262,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1605848445044691</v>
+        <v>0.1621348445044691</v>
       </c>
       <c r="C72">
-        <v>-0.2221005611077085</v>
+        <v>-0.2867563282318333</v>
       </c>
       <c r="D72">
-        <v>2.458045096183542</v>
+        <v>2.440377124163577</v>
       </c>
       <c r="E72">
-        <v>1.890366146875179</v>
+        <v>1.937353941979339</v>
       </c>
       <c r="F72">
-        <v>3.28914565729125</v>
+        <v>3.336133452395411</v>
       </c>
       <c r="G72">
         <v>0.609</v>
@@ -7298,37 +7298,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M72">
-        <v>0.6604604479840831</v>
+        <v>0.6698955972409985</v>
       </c>
       <c r="N72">
-        <v>-0.306460447984083</v>
+        <v>-0.3158955972409983</v>
       </c>
       <c r="O72">
-        <v>-0.09193813439522489</v>
+        <v>-0.09476867917229949</v>
       </c>
       <c r="P72">
-        <v>-0.2145223135888581</v>
+        <v>-0.2211269180686988</v>
       </c>
       <c r="Q72">
-        <v>0.2014776864111419</v>
+        <v>0.1948730819313012</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1420881944718247</v>
+        <v>0.1454084770398187</v>
       </c>
       <c r="T72">
-        <v>2.223745830758078</v>
+        <v>2.300426721473873</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1607969111915078</v>
+        <v>0.1585321659634584</v>
       </c>
       <c r="W72">
-        <v>0.1685119802327452</v>
+        <v>0.1689667410745375</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5359897039716925</v>
+        <v>0.5284405532115279</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7344,22 +7344,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1621348445044691</v>
+        <v>0.1636848445044691</v>
       </c>
       <c r="C73">
-        <v>-0.2867563282318328</v>
+        <v>-0.3511599197389144</v>
       </c>
       <c r="D73">
-        <v>2.440377124163577</v>
+        <v>2.422961327760657</v>
       </c>
       <c r="E73">
-        <v>1.937353941979339</v>
+        <v>1.9843417370835</v>
       </c>
       <c r="F73">
-        <v>3.33613345239541</v>
+        <v>3.383121247499571</v>
       </c>
       <c r="G73">
         <v>0.609</v>
@@ -7380,37 +7380,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M73">
-        <v>0.6698955972409985</v>
+        <v>0.6793307464979139</v>
       </c>
       <c r="N73">
-        <v>-0.3158955972409983</v>
+        <v>-0.3253307464979138</v>
       </c>
       <c r="O73">
-        <v>-0.09476867917229949</v>
+        <v>-0.09759922394937413</v>
       </c>
       <c r="P73">
-        <v>-0.2211269180686988</v>
+        <v>-0.2277315225485396</v>
       </c>
       <c r="Q73">
-        <v>0.1948730819313012</v>
+        <v>0.1882684774514604</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1454084770398187</v>
+        <v>0.1489659226483836</v>
       </c>
       <c r="T73">
-        <v>2.300426721473873</v>
+        <v>2.382584818669368</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1585321659634584</v>
+        <v>0.156330330325077</v>
       </c>
       <c r="W73">
-        <v>0.1689667410745375</v>
+        <v>0.1694088696707245</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5284405532115279</v>
+        <v>0.5211011010835901</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7426,22 +7426,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1636848445044691</v>
+        <v>0.1652348445044691</v>
       </c>
       <c r="C74">
-        <v>-0.3511599197389144</v>
+        <v>-0.415316696339981</v>
       </c>
       <c r="D74">
-        <v>2.422961327760657</v>
+        <v>2.405792346263751</v>
       </c>
       <c r="E74">
-        <v>1.9843417370835</v>
+        <v>2.031329532187661</v>
       </c>
       <c r="F74">
-        <v>3.383121247499571</v>
+        <v>3.430109042603732</v>
       </c>
       <c r="G74">
         <v>0.609</v>
@@ -7462,37 +7462,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M74">
-        <v>0.6793307464979139</v>
+        <v>0.6887658957548294</v>
       </c>
       <c r="N74">
-        <v>-0.3253307464979138</v>
+        <v>-0.3347658957548292</v>
       </c>
       <c r="O74">
-        <v>-0.09759922394937413</v>
+        <v>-0.1004297687264488</v>
       </c>
       <c r="P74">
-        <v>-0.2277315225485396</v>
+        <v>-0.2343361270283805</v>
       </c>
       <c r="Q74">
-        <v>0.1882684774514604</v>
+        <v>0.1816638729716195</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1489659226483836</v>
+        <v>0.1527868827464719</v>
       </c>
       <c r="T74">
-        <v>2.382584818669368</v>
+        <v>2.470828700842308</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.156330330325077</v>
+        <v>0.1541888189507609</v>
       </c>
       <c r="W74">
-        <v>0.1694088696707245</v>
+        <v>0.1698388851546872</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5211011010835901</v>
+        <v>0.5139627298358697</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7508,22 +7508,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1652348445044691</v>
+        <v>0.1667848445044691</v>
       </c>
       <c r="C75">
-        <v>-0.415316696339981</v>
+        <v>-0.4792318678722336</v>
       </c>
       <c r="D75">
-        <v>2.405792346263751</v>
+        <v>2.388864969835659</v>
       </c>
       <c r="E75">
-        <v>2.031329532187661</v>
+        <v>2.078317327291821</v>
       </c>
       <c r="F75">
-        <v>3.430109042603732</v>
+        <v>3.477096837707893</v>
       </c>
       <c r="G75">
         <v>0.609</v>
@@ -7544,37 +7544,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M75">
-        <v>0.6887658957548294</v>
+        <v>0.6982010450117448</v>
       </c>
       <c r="N75">
-        <v>-0.3347658957548292</v>
+        <v>-0.3442010450117447</v>
       </c>
       <c r="O75">
-        <v>-0.1004297687264488</v>
+        <v>-0.1032603135035234</v>
       </c>
       <c r="P75">
-        <v>-0.2343361270283805</v>
+        <v>-0.2409407315082213</v>
       </c>
       <c r="Q75">
-        <v>0.1816638729716195</v>
+        <v>0.1750592684917787</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1527868827464719</v>
+        <v>0.1569017628521054</v>
       </c>
       <c r="T75">
-        <v>2.470828700842308</v>
+        <v>2.565860573951627</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1541888189507609</v>
+        <v>0.1521051862622371</v>
       </c>
       <c r="W75">
-        <v>0.1698388851546872</v>
+        <v>0.1702572785985428</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5139627298358697</v>
+        <v>0.5070172875407903</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7590,22 +7590,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1667848445044691</v>
+        <v>0.1683348445044691</v>
       </c>
       <c r="C76">
-        <v>-0.4792318678722336</v>
+        <v>-0.5429104985697744</v>
       </c>
       <c r="D76">
-        <v>2.388864969835659</v>
+        <v>2.372174134242279</v>
       </c>
       <c r="E76">
-        <v>2.078317327291821</v>
+        <v>2.125305122395982</v>
       </c>
       <c r="F76">
-        <v>3.477096837707893</v>
+        <v>3.524084632812054</v>
       </c>
       <c r="G76">
         <v>0.609</v>
@@ -7626,37 +7626,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M76">
-        <v>0.6982010450117448</v>
+        <v>0.7076361942686604</v>
       </c>
       <c r="N76">
-        <v>-0.3442010450117447</v>
+        <v>-0.3536361942686603</v>
       </c>
       <c r="O76">
-        <v>-0.1032603135035234</v>
+        <v>-0.1060908582805981</v>
       </c>
       <c r="P76">
-        <v>-0.2409407315082213</v>
+        <v>-0.2475453359880622</v>
       </c>
       <c r="Q76">
-        <v>0.1750592684917787</v>
+        <v>0.1684546640119378</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1569017628521054</v>
+        <v>0.1613458333661897</v>
       </c>
       <c r="T76">
-        <v>2.565860573951627</v>
+        <v>2.668494996909692</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1521051862622371</v>
+        <v>0.1500771171120739</v>
       </c>
       <c r="W76">
-        <v>0.1702572785985428</v>
+        <v>0.1706645148838956</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5070172875407903</v>
+        <v>0.5002570570402465</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7672,22 +7672,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1683348445044691</v>
+        <v>0.1970286633147041</v>
       </c>
       <c r="C77">
-        <v>-0.5429104985697744</v>
+        <v>-0.8615821352647468</v>
       </c>
       <c r="D77">
-        <v>2.372174134242279</v>
+        <v>2.100490292651467</v>
       </c>
       <c r="E77">
-        <v>2.125305122395982</v>
+        <v>2.172292917500143</v>
       </c>
       <c r="F77">
-        <v>3.524084632812054</v>
+        <v>3.571072427916214</v>
       </c>
       <c r="G77">
         <v>0.609</v>
@@ -7708,45 +7708,45 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M77">
-        <v>0.7076361942686604</v>
+        <v>0.8420588785026433</v>
       </c>
       <c r="N77">
-        <v>-0.3536361942686603</v>
+        <v>-0.4880588785026431</v>
       </c>
       <c r="O77">
-        <v>-0.1060908582805981</v>
+        <v>-0.1464176635507929</v>
       </c>
       <c r="P77">
-        <v>-0.2475453359880622</v>
+        <v>-0.3416412149518502</v>
       </c>
       <c r="Q77">
-        <v>0.1684546640119378</v>
+        <v>0.0743587850481498</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1613458333661897</v>
+        <v>0.1684261547990937</v>
       </c>
       <c r="T77">
-        <v>2.668494996909692</v>
+        <v>2.832012812912095</v>
       </c>
       <c r="U77">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1500771171120739</v>
+        <v>0.1261194468833888</v>
       </c>
       <c r="W77">
-        <v>0.1706645148838956</v>
+        <v>0.2060610344248969</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5002570570402465</v>
+        <v>0.4203981562779626</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7754,22 +7754,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1970286633147041</v>
+        <v>0.1989286633147042</v>
       </c>
       <c r="C78">
-        <v>-0.8615821352647468</v>
+        <v>-0.9243795720969117</v>
       </c>
       <c r="D78">
-        <v>2.100490292651467</v>
+        <v>2.084680650923463</v>
       </c>
       <c r="E78">
-        <v>2.172292917500143</v>
+        <v>2.219280712604303</v>
       </c>
       <c r="F78">
-        <v>3.571072427916214</v>
+        <v>3.618060223020375</v>
       </c>
       <c r="G78">
         <v>0.609</v>
@@ -7790,37 +7790,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M78">
-        <v>0.8420588785026433</v>
+        <v>0.8531386005882045</v>
       </c>
       <c r="N78">
-        <v>-0.4880588785026431</v>
+        <v>-0.4991386005882043</v>
       </c>
       <c r="O78">
-        <v>-0.1464176635507929</v>
+        <v>-0.1497415801764613</v>
       </c>
       <c r="P78">
-        <v>-0.3416412149518502</v>
+        <v>-0.349397020411743</v>
       </c>
       <c r="Q78">
-        <v>0.0743587850481498</v>
+        <v>0.06660297958825695</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1684261547990937</v>
+        <v>0.1737577267468804</v>
       </c>
       <c r="T78">
-        <v>2.832012812912095</v>
+        <v>2.955143804777839</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1261194468833888</v>
+        <v>0.1244815319887993</v>
       </c>
       <c r="W78">
-        <v>0.2060610344248969</v>
+        <v>0.2064472547570411</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4203981562779626</v>
+        <v>0.4149384399626643</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7836,22 +7836,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1989286633147042</v>
+        <v>0.2008286633147041</v>
       </c>
       <c r="C79">
-        <v>-0.9243795720969117</v>
+        <v>-0.9869407997155264</v>
       </c>
       <c r="D79">
-        <v>2.084680650923463</v>
+        <v>2.069107218409009</v>
       </c>
       <c r="E79">
-        <v>2.219280712604303</v>
+        <v>2.266268507708464</v>
       </c>
       <c r="F79">
-        <v>3.618060223020375</v>
+        <v>3.665048018124536</v>
       </c>
       <c r="G79">
         <v>0.609</v>
@@ -7872,37 +7872,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M79">
-        <v>0.8531386005882045</v>
+        <v>0.8642183226737655</v>
       </c>
       <c r="N79">
-        <v>-0.4991386005882043</v>
+        <v>-0.5102183226737653</v>
       </c>
       <c r="O79">
-        <v>-0.1497415801764613</v>
+        <v>-0.1530654968021296</v>
       </c>
       <c r="P79">
-        <v>-0.349397020411743</v>
+        <v>-0.3571528258716358</v>
       </c>
       <c r="Q79">
-        <v>0.06660297958825695</v>
+        <v>0.05884717412836421</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1737577267468804</v>
+        <v>0.1795739870535568</v>
       </c>
       <c r="T79">
-        <v>2.955143804777839</v>
+        <v>3.089468523176831</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1244815319887993</v>
+        <v>0.1228856149120198</v>
       </c>
       <c r="W79">
-        <v>0.2064472547570411</v>
+        <v>0.2068235720037457</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4149384399626643</v>
+        <v>0.4096187163733995</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7918,22 +7918,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2008286633147041</v>
+        <v>0.2027286633147042</v>
       </c>
       <c r="C80">
-        <v>-0.9869407997155264</v>
+        <v>-1.049271072610907</v>
       </c>
       <c r="D80">
-        <v>2.069107218409009</v>
+        <v>2.05376474061779</v>
       </c>
       <c r="E80">
-        <v>2.266268507708464</v>
+        <v>2.313256302812625</v>
       </c>
       <c r="F80">
-        <v>3.665048018124536</v>
+        <v>3.712035813228697</v>
       </c>
       <c r="G80">
         <v>0.609</v>
@@ -7954,37 +7954,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M80">
-        <v>0.8642183226737655</v>
+        <v>0.8752980447593267</v>
       </c>
       <c r="N80">
-        <v>-0.5102183226737653</v>
+        <v>-0.5212980447593265</v>
       </c>
       <c r="O80">
-        <v>-0.1530654968021296</v>
+        <v>-0.1563894134277979</v>
       </c>
       <c r="P80">
-        <v>-0.3571528258716358</v>
+        <v>-0.3649086313315286</v>
       </c>
       <c r="Q80">
-        <v>0.05884717412836421</v>
+        <v>0.05109136866847142</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1795739870535568</v>
+        <v>0.18594417691325</v>
       </c>
       <c r="T80">
-        <v>3.089468523176831</v>
+        <v>3.236586071899538</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1228856149120198</v>
+        <v>0.1213301007992094</v>
       </c>
       <c r="W80">
-        <v>0.2068235720037457</v>
+        <v>0.2071903622315464</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4096187163733995</v>
+        <v>0.4044336693306982</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8000,22 +8000,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2027286633147042</v>
+        <v>0.2046286633147042</v>
       </c>
       <c r="C81">
-        <v>-1.049271072610907</v>
+        <v>-1.111375490571812</v>
       </c>
       <c r="D81">
-        <v>2.05376474061779</v>
+        <v>2.038648117761045</v>
       </c>
       <c r="E81">
-        <v>2.313256302812625</v>
+        <v>2.360244097916786</v>
       </c>
       <c r="F81">
-        <v>3.712035813228697</v>
+        <v>3.759023608332857</v>
       </c>
       <c r="G81">
         <v>0.609</v>
@@ -8036,37 +8036,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M81">
-        <v>0.8752980447593267</v>
+        <v>0.8863777668448877</v>
       </c>
       <c r="N81">
-        <v>-0.5212980447593265</v>
+        <v>-0.5323777668448875</v>
       </c>
       <c r="O81">
-        <v>-0.1563894134277979</v>
+        <v>-0.1597133300534662</v>
       </c>
       <c r="P81">
-        <v>-0.3649086313315286</v>
+        <v>-0.3726644367914212</v>
       </c>
       <c r="Q81">
-        <v>0.05109136866847142</v>
+        <v>0.04333556320857873</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.18594417691325</v>
+        <v>0.1929513857589125</v>
       </c>
       <c r="T81">
-        <v>3.236586071899538</v>
+        <v>3.398415375494515</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1213301007992094</v>
+        <v>0.1198134745392193</v>
       </c>
       <c r="W81">
-        <v>0.2071903622315464</v>
+        <v>0.2075479827036521</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4044336693306982</v>
+        <v>0.3993782484640646</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8082,22 +8082,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2046286633147042</v>
+        <v>0.2065286633147042</v>
       </c>
       <c r="C82">
-        <v>-1.111375490571812</v>
+        <v>-1.173259004337217</v>
       </c>
       <c r="D82">
-        <v>2.038648117761045</v>
+        <v>2.023752399099801</v>
       </c>
       <c r="E82">
-        <v>2.360244097916786</v>
+        <v>2.407231893020946</v>
       </c>
       <c r="F82">
-        <v>3.759023608332857</v>
+        <v>3.806011403437018</v>
       </c>
       <c r="G82">
         <v>0.609</v>
@@ -8118,37 +8118,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M82">
-        <v>0.8863777668448877</v>
+        <v>0.8974574889304489</v>
       </c>
       <c r="N82">
-        <v>-0.5323777668448875</v>
+        <v>-0.5434574889304487</v>
       </c>
       <c r="O82">
-        <v>-0.1597133300534662</v>
+        <v>-0.1630372466791346</v>
       </c>
       <c r="P82">
-        <v>-0.3726644367914212</v>
+        <v>-0.3804202422513141</v>
       </c>
       <c r="Q82">
-        <v>0.04333556320857873</v>
+        <v>0.03557975774868588</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1929513857589125</v>
+        <v>0.2006961955356973</v>
       </c>
       <c r="T82">
-        <v>3.398415375494515</v>
+        <v>3.577279342625805</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1198134745392193</v>
+        <v>0.1183342958412043</v>
       </c>
       <c r="W82">
-        <v>0.2075479827036521</v>
+        <v>0.2078967730406441</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3993782484640646</v>
+        <v>0.3944476528040143</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8164,22 +8164,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2065286633147042</v>
+        <v>0.2084286633147042</v>
       </c>
       <c r="C83">
-        <v>-1.173259004337217</v>
+        <v>-1.234926421002088</v>
       </c>
       <c r="D83">
-        <v>2.023752399099801</v>
+        <v>2.00907277753909</v>
       </c>
       <c r="E83">
-        <v>2.407231893020946</v>
+        <v>2.454219688125107</v>
       </c>
       <c r="F83">
-        <v>3.806011403437018</v>
+        <v>3.852999198541179</v>
       </c>
       <c r="G83">
         <v>0.609</v>
@@ -8200,37 +8200,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M83">
-        <v>0.8974574889304489</v>
+        <v>0.9085372110160099</v>
       </c>
       <c r="N83">
-        <v>-0.5434574889304487</v>
+        <v>-0.5545372110160098</v>
       </c>
       <c r="O83">
-        <v>-0.1630372466791346</v>
+        <v>-0.1663611633048029</v>
       </c>
       <c r="P83">
-        <v>-0.3804202422513141</v>
+        <v>-0.3881760477112069</v>
       </c>
       <c r="Q83">
-        <v>0.03557975774868588</v>
+        <v>0.02782395228879309</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2006961955356973</v>
+        <v>0.209301539732125</v>
       </c>
       <c r="T83">
-        <v>3.577279342625805</v>
+        <v>3.776017083882795</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1183342958412043</v>
+        <v>0.1168911946724091</v>
       </c>
       <c r="W83">
-        <v>0.2078967730406441</v>
+        <v>0.2082370562962459</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3944476528040143</v>
+        <v>0.3896373155746969</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8246,22 +8246,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2084286633147042</v>
+        <v>0.2103286633147042</v>
       </c>
       <c r="C84">
-        <v>-1.234926421002088</v>
+        <v>-1.296382409189599</v>
       </c>
       <c r="D84">
-        <v>2.00907277753909</v>
+        <v>1.99460458445574</v>
       </c>
       <c r="E84">
-        <v>2.454219688125107</v>
+        <v>2.501207483229268</v>
       </c>
       <c r="F84">
-        <v>3.852999198541179</v>
+        <v>3.89998699364534</v>
       </c>
       <c r="G84">
         <v>0.609</v>
@@ -8282,37 +8282,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M84">
-        <v>0.9085372110160099</v>
+        <v>0.9196169331015711</v>
       </c>
       <c r="N84">
-        <v>-0.5545372110160098</v>
+        <v>-0.565616933101571</v>
       </c>
       <c r="O84">
-        <v>-0.1663611633048029</v>
+        <v>-0.1696850799304713</v>
       </c>
       <c r="P84">
-        <v>-0.3881760477112069</v>
+        <v>-0.3959318531710997</v>
       </c>
       <c r="Q84">
-        <v>0.02782395228879309</v>
+        <v>0.02006814682890029</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.209301539732125</v>
+        <v>0.2189192773634265</v>
       </c>
       <c r="T84">
-        <v>3.776017083882795</v>
+        <v>3.998135735875901</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1168911946724091</v>
+        <v>0.1154828670257536</v>
       </c>
       <c r="W84">
-        <v>0.2082370562962459</v>
+        <v>0.2085691399553273</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3896373155746969</v>
+        <v>0.3849428900858451</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8328,22 +8328,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2103286633147042</v>
+        <v>0.2122286633147042</v>
       </c>
       <c r="C85">
-        <v>-1.296382409189599</v>
+        <v>-1.357631504001451</v>
       </c>
       <c r="D85">
-        <v>1.99460458445574</v>
+        <v>1.980343284748049</v>
       </c>
       <c r="E85">
-        <v>2.501207483229268</v>
+        <v>2.548195278333429</v>
       </c>
       <c r="F85">
-        <v>3.89998699364534</v>
+        <v>3.9469747887495</v>
       </c>
       <c r="G85">
         <v>0.609</v>
@@ -8364,37 +8364,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M85">
-        <v>0.9196169331015711</v>
+        <v>0.9306966551871322</v>
       </c>
       <c r="N85">
-        <v>-0.565616933101571</v>
+        <v>-0.576696655187132</v>
       </c>
       <c r="O85">
-        <v>-0.1696850799304713</v>
+        <v>-0.1730089965561396</v>
       </c>
       <c r="P85">
-        <v>-0.3959318531710997</v>
+        <v>-0.4036876586309924</v>
       </c>
       <c r="Q85">
-        <v>0.02006814682890029</v>
+        <v>0.01231234136900755</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2189192773634265</v>
+        <v>0.2297392321986406</v>
       </c>
       <c r="T85">
-        <v>3.998135735875901</v>
+        <v>4.248019219368145</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1154828670257536</v>
+        <v>0.1141080709897327</v>
       </c>
       <c r="W85">
-        <v>0.2085691399553273</v>
+        <v>0.208893316860621</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3849428900858451</v>
+        <v>0.3803602366324423</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8410,22 +8410,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2122286633147041</v>
+        <v>0.2141286633147041</v>
       </c>
       <c r="C86">
-        <v>-1.35763150400145</v>
+        <v>-1.418678111757342</v>
       </c>
       <c r="D86">
-        <v>1.980343284748049</v>
+        <v>1.966284472096318</v>
       </c>
       <c r="E86">
-        <v>2.548195278333428</v>
+        <v>2.595183073437589</v>
       </c>
       <c r="F86">
-        <v>3.946974788749499</v>
+        <v>3.99396258385366</v>
       </c>
       <c r="G86">
         <v>0.609</v>
@@ -8446,37 +8446,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M86">
-        <v>0.930696655187132</v>
+        <v>0.9417763772726931</v>
       </c>
       <c r="N86">
-        <v>-0.5766966551871318</v>
+        <v>-0.5877763772726929</v>
       </c>
       <c r="O86">
-        <v>-0.1730089965561395</v>
+        <v>-0.1763329131818079</v>
       </c>
       <c r="P86">
-        <v>-0.4036876586309922</v>
+        <v>-0.4114434640908851</v>
       </c>
       <c r="Q86">
-        <v>0.01231234136900777</v>
+        <v>0.004556535909114923</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2297392321986405</v>
+        <v>0.2420018476785499</v>
       </c>
       <c r="T86">
-        <v>4.248019219368142</v>
+        <v>4.531220500659352</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1141080709897327</v>
+        <v>0.1127656230957358</v>
       </c>
       <c r="W86">
-        <v>0.208893316860621</v>
+        <v>0.2092098660740255</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3803602366324424</v>
+        <v>0.3758854103191196</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8492,22 +8492,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2141286633147041</v>
+        <v>0.2160286633147042</v>
       </c>
       <c r="C87">
-        <v>-1.418678111757342</v>
+        <v>-1.479526514533973</v>
       </c>
       <c r="D87">
-        <v>1.966284472096318</v>
+        <v>1.952423864423849</v>
       </c>
       <c r="E87">
-        <v>2.595183073437589</v>
+        <v>2.64217086854175</v>
       </c>
       <c r="F87">
-        <v>3.99396258385366</v>
+        <v>4.040950378957821</v>
       </c>
       <c r="G87">
         <v>0.609</v>
@@ -8528,37 +8528,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M87">
-        <v>0.9417763772726931</v>
+        <v>0.9528560993582542</v>
       </c>
       <c r="N87">
-        <v>-0.5877763772726929</v>
+        <v>-0.5988560993582541</v>
       </c>
       <c r="O87">
-        <v>-0.1763329131818079</v>
+        <v>-0.1796568298074762</v>
       </c>
       <c r="P87">
-        <v>-0.4114434640908851</v>
+        <v>-0.4191992695507779</v>
       </c>
       <c r="Q87">
-        <v>0.004556535909114923</v>
+        <v>-0.003199269550777928</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2420018476785499</v>
+        <v>0.2560162653698749</v>
       </c>
       <c r="T87">
-        <v>4.531220500659352</v>
+        <v>4.854879107849306</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1127656230957358</v>
+        <v>0.1114543949202041</v>
       </c>
       <c r="W87">
-        <v>0.2092098660740255</v>
+        <v>0.2095190536778159</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3758854103191196</v>
+        <v>0.3715146497340134</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8574,22 +8574,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2160286633147042</v>
+        <v>0.2179286633147042</v>
       </c>
       <c r="C88">
-        <v>-1.479526514533973</v>
+        <v>-1.540180874513424</v>
       </c>
       <c r="D88">
-        <v>1.952423864423849</v>
+        <v>1.938757299548558</v>
       </c>
       <c r="E88">
-        <v>2.64217086854175</v>
+        <v>2.689158663645911</v>
       </c>
       <c r="F88">
-        <v>4.040950378957821</v>
+        <v>4.087938174061982</v>
       </c>
       <c r="G88">
         <v>0.609</v>
@@ -8610,37 +8610,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M88">
-        <v>0.9528560993582542</v>
+        <v>0.9639358214438154</v>
       </c>
       <c r="N88">
-        <v>-0.5988560993582541</v>
+        <v>-0.6099358214438153</v>
       </c>
       <c r="O88">
-        <v>-0.1796568298074762</v>
+        <v>-0.1829807464331446</v>
       </c>
       <c r="P88">
-        <v>-0.4191992695507779</v>
+        <v>-0.4269550750106708</v>
       </c>
       <c r="Q88">
-        <v>-0.003199269550777928</v>
+        <v>-0.01095507501067078</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2560162653698749</v>
+        <v>0.2721867473214037</v>
       </c>
       <c r="T88">
-        <v>4.854879107849306</v>
+        <v>5.228331346914636</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1114543949202041</v>
+        <v>0.1101733099211212</v>
       </c>
       <c r="W88">
-        <v>0.2095190536778159</v>
+        <v>0.2098211335205996</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3715146497340134</v>
+        <v>0.3672443664037374</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8656,22 +8656,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2179286633147042</v>
+        <v>0.2198286633147042</v>
       </c>
       <c r="C89">
-        <v>-1.540180874513424</v>
+        <v>-1.600645238150175</v>
       </c>
       <c r="D89">
-        <v>1.938757299548558</v>
+        <v>1.925280731015967</v>
       </c>
       <c r="E89">
-        <v>2.689158663645911</v>
+        <v>2.736146458750071</v>
       </c>
       <c r="F89">
-        <v>4.087938174061982</v>
+        <v>4.134925969166143</v>
       </c>
       <c r="G89">
         <v>0.609</v>
@@ -8692,37 +8692,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M89">
-        <v>0.9639358214438154</v>
+        <v>0.9750155435293765</v>
       </c>
       <c r="N89">
-        <v>-0.6099358214438153</v>
+        <v>-0.6210155435293763</v>
       </c>
       <c r="O89">
-        <v>-0.1829807464331446</v>
+        <v>-0.1863046630588129</v>
       </c>
       <c r="P89">
-        <v>-0.4269550750106708</v>
+        <v>-0.4347108804705634</v>
       </c>
       <c r="Q89">
-        <v>-0.01095507501067078</v>
+        <v>-0.01871088047056341</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2721867473214037</v>
+        <v>0.2910523095981874</v>
       </c>
       <c r="T89">
-        <v>5.228331346914636</v>
+        <v>5.66402562582419</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1101733099211212</v>
+        <v>0.1089213404901994</v>
       </c>
       <c r="W89">
-        <v>0.2098211335205996</v>
+        <v>0.210116347912411</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3672443664037374</v>
+        <v>0.3630711349673313</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8738,22 +8738,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2198286633147042</v>
+        <v>0.2217286633147042</v>
       </c>
       <c r="C90">
-        <v>-1.600645238150175</v>
+        <v>-1.660923540165538</v>
       </c>
       <c r="D90">
-        <v>1.925280731015967</v>
+        <v>1.911990224104765</v>
       </c>
       <c r="E90">
-        <v>2.736146458750071</v>
+        <v>2.783134253854232</v>
       </c>
       <c r="F90">
-        <v>4.134925969166143</v>
+        <v>4.181913764270304</v>
       </c>
       <c r="G90">
         <v>0.609</v>
@@ -8774,37 +8774,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M90">
-        <v>0.9750155435293765</v>
+        <v>0.9860952656149377</v>
       </c>
       <c r="N90">
-        <v>-0.6210155435293763</v>
+        <v>-0.6320952656149375</v>
       </c>
       <c r="O90">
-        <v>-0.1863046630588129</v>
+        <v>-0.1896285796844812</v>
       </c>
       <c r="P90">
-        <v>-0.4347108804705634</v>
+        <v>-0.4424666859304562</v>
       </c>
       <c r="Q90">
-        <v>-0.01871088047056341</v>
+        <v>-0.02646668593045626</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2910523095981874</v>
+        <v>0.3133479741071136</v>
       </c>
       <c r="T90">
-        <v>5.66402562582419</v>
+        <v>6.178937046353663</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1089213404901994</v>
+        <v>0.1076975052037926</v>
       </c>
       <c r="W90">
-        <v>0.210116347912411</v>
+        <v>0.2104049282729457</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3630711349673313</v>
+        <v>0.3589916840126423</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8820,22 +8820,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2217286633147042</v>
+        <v>0.2236286633147042</v>
       </c>
       <c r="C91">
-        <v>-1.660923540165538</v>
+        <v>-1.721019607377762</v>
       </c>
       <c r="D91">
-        <v>1.911990224104765</v>
+        <v>1.898881951996702</v>
       </c>
       <c r="E91">
-        <v>2.783134253854232</v>
+        <v>2.830122048958393</v>
       </c>
       <c r="F91">
-        <v>4.181913764270304</v>
+        <v>4.228901559374465</v>
       </c>
       <c r="G91">
         <v>0.609</v>
@@ -8856,37 +8856,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M91">
-        <v>0.9860952656149377</v>
+        <v>0.9971749877004987</v>
       </c>
       <c r="N91">
-        <v>-0.6320952656149375</v>
+        <v>-0.6431749877004986</v>
       </c>
       <c r="O91">
-        <v>-0.1896285796844812</v>
+        <v>-0.1929524963101496</v>
       </c>
       <c r="P91">
-        <v>-0.4424666859304562</v>
+        <v>-0.4502224913903491</v>
       </c>
       <c r="Q91">
-        <v>-0.02646668593045626</v>
+        <v>-0.03422249139034911</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3133479741071136</v>
+        <v>0.3401027715178249</v>
       </c>
       <c r="T91">
-        <v>6.178937046353663</v>
+        <v>6.796830750989029</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1076975052037926</v>
+        <v>0.1065008662570838</v>
       </c>
       <c r="W91">
-        <v>0.2104049282729457</v>
+        <v>0.2106870957365796</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3589916840126423</v>
+        <v>0.3550028875236128</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8902,22 +8902,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2236286633147042</v>
+        <v>0.2255286633147042</v>
       </c>
       <c r="C92">
-        <v>-1.721019607377762</v>
+        <v>-1.78093716237568</v>
       </c>
       <c r="D92">
-        <v>1.898881951996702</v>
+        <v>1.885952192102946</v>
       </c>
       <c r="E92">
-        <v>2.830122048958393</v>
+        <v>2.877109844062554</v>
       </c>
       <c r="F92">
-        <v>4.228901559374465</v>
+        <v>4.275889354478625</v>
       </c>
       <c r="G92">
         <v>0.609</v>
@@ -8938,37 +8938,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M92">
-        <v>0.9971749877004987</v>
+        <v>1.00825470978606</v>
       </c>
       <c r="N92">
-        <v>-0.6431749877004986</v>
+        <v>-0.6542547097860598</v>
       </c>
       <c r="O92">
-        <v>-0.1929524963101496</v>
+        <v>-0.1962764129358179</v>
       </c>
       <c r="P92">
-        <v>-0.4502224913903491</v>
+        <v>-0.4579782968502419</v>
       </c>
       <c r="Q92">
-        <v>-0.03422249139034911</v>
+        <v>-0.0419782968502419</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3401027715178249</v>
+        <v>0.37280307946425</v>
       </c>
       <c r="T92">
-        <v>6.796830750989029</v>
+        <v>7.55203416776559</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1065008662570838</v>
+        <v>0.1053305270674455</v>
       </c>
       <c r="W92">
-        <v>0.2106870957365796</v>
+        <v>0.2109630617174963</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3550028875236128</v>
+        <v>0.3511017568914852</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8984,22 +8984,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2255286633147042</v>
+        <v>0.2274286633147042</v>
       </c>
       <c r="C93">
-        <v>-1.78093716237568</v>
+        <v>-1.840679827043266</v>
       </c>
       <c r="D93">
-        <v>1.885952192102946</v>
+        <v>1.873197322539519</v>
       </c>
       <c r="E93">
-        <v>2.877109844062554</v>
+        <v>2.924097639166714</v>
       </c>
       <c r="F93">
-        <v>4.275889354478625</v>
+        <v>4.322877149582785</v>
       </c>
       <c r="G93">
         <v>0.609</v>
@@ -9020,37 +9020,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M93">
-        <v>1.00825470978606</v>
+        <v>1.019334431871621</v>
       </c>
       <c r="N93">
-        <v>-0.6542547097860598</v>
+        <v>-0.6653344318716208</v>
       </c>
       <c r="O93">
-        <v>-0.1962764129358179</v>
+        <v>-0.1996003295614862</v>
       </c>
       <c r="P93">
-        <v>-0.4579782968502419</v>
+        <v>-0.4657341023101346</v>
       </c>
       <c r="Q93">
-        <v>-0.0419782968502419</v>
+        <v>-0.04973410231013459</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.37280307946425</v>
+        <v>0.4136784643972813</v>
       </c>
       <c r="T93">
-        <v>7.55203416776559</v>
+        <v>8.49603843873629</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1053305270674455</v>
+        <v>0.1041856300341038</v>
       </c>
       <c r="W93">
-        <v>0.2109630617174963</v>
+        <v>0.2112330284379584</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3511017568914852</v>
+        <v>0.3472854334470125</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9066,22 +9066,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2274286633147042</v>
+        <v>0.2293286633147042</v>
       </c>
       <c r="C94">
-        <v>-1.840679827043266</v>
+        <v>-1.900251125942154</v>
       </c>
       <c r="D94">
-        <v>1.873197322539519</v>
+        <v>1.860613818744793</v>
       </c>
       <c r="E94">
-        <v>2.924097639166714</v>
+        <v>2.971085434270875</v>
       </c>
       <c r="F94">
-        <v>4.322877149582785</v>
+        <v>4.369864944686946</v>
       </c>
       <c r="G94">
         <v>0.609</v>
@@ -9102,37 +9102,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M94">
-        <v>1.019334431871621</v>
+        <v>1.030414153957182</v>
       </c>
       <c r="N94">
-        <v>-0.6653344318716208</v>
+        <v>-0.676414153957182</v>
       </c>
       <c r="O94">
-        <v>-0.1996003295614862</v>
+        <v>-0.2029242461871546</v>
       </c>
       <c r="P94">
-        <v>-0.4657341023101346</v>
+        <v>-0.4734899077700274</v>
       </c>
       <c r="Q94">
-        <v>-0.04973410231013459</v>
+        <v>-0.05748990777002744</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4136784643972813</v>
+        <v>0.46623253073975</v>
       </c>
       <c r="T94">
-        <v>8.49603843873629</v>
+        <v>9.709758215698617</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1041856300341038</v>
+        <v>0.1030653544423392</v>
       </c>
       <c r="W94">
-        <v>0.2112330284379584</v>
+        <v>0.2114971894224964</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3472854334470125</v>
+        <v>0.343551181474464</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9148,22 +9148,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2293286633147042</v>
+        <v>0.2312286633147042</v>
       </c>
       <c r="C95">
-        <v>-1.900251125942154</v>
+        <v>-1.959654489558699</v>
       </c>
       <c r="D95">
-        <v>1.860613818744793</v>
+        <v>1.848198250232408</v>
       </c>
       <c r="E95">
-        <v>2.971085434270875</v>
+        <v>3.018073229375036</v>
       </c>
       <c r="F95">
-        <v>4.369864944686946</v>
+        <v>4.416852739791107</v>
       </c>
       <c r="G95">
         <v>0.609</v>
@@ -9184,37 +9184,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M95">
-        <v>1.030414153957182</v>
+        <v>1.041493876042743</v>
       </c>
       <c r="N95">
-        <v>-0.676414153957182</v>
+        <v>-0.6874938760427429</v>
       </c>
       <c r="O95">
-        <v>-0.2029242461871546</v>
+        <v>-0.2062481628128229</v>
       </c>
       <c r="P95">
-        <v>-0.4734899077700274</v>
+        <v>-0.48124571322992</v>
       </c>
       <c r="Q95">
-        <v>-0.05748990777002744</v>
+        <v>-0.06524571322992007</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.46623253073975</v>
+        <v>0.5363046191963752</v>
       </c>
       <c r="T95">
-        <v>9.709758215698617</v>
+        <v>11.32805125164839</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1030653544423392</v>
+        <v>0.1019689145014633</v>
       </c>
       <c r="W95">
-        <v>0.2114971894224964</v>
+        <v>0.211755729960555</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.343551181474464</v>
+        <v>0.3398963816715441</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9230,22 +9230,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2312286633147042</v>
+        <v>0.2331286633147042</v>
       </c>
       <c r="C96">
-        <v>-1.959654489558699</v>
+        <v>-2.018893257421932</v>
       </c>
       <c r="D96">
-        <v>1.848198250232408</v>
+        <v>1.835947277473335</v>
       </c>
       <c r="E96">
-        <v>3.018073229375036</v>
+        <v>3.065061024479196</v>
       </c>
       <c r="F96">
-        <v>4.416852739791107</v>
+        <v>4.463840534895268</v>
       </c>
       <c r="G96">
         <v>0.609</v>
@@ -9266,37 +9266,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M96">
-        <v>1.041493876042743</v>
+        <v>1.052573598128304</v>
       </c>
       <c r="N96">
-        <v>-0.6874938760427429</v>
+        <v>-0.6985735981283041</v>
       </c>
       <c r="O96">
-        <v>-0.2062481628128229</v>
+        <v>-0.2095720794384912</v>
       </c>
       <c r="P96">
-        <v>-0.48124571322992</v>
+        <v>-0.4890015186898129</v>
       </c>
       <c r="Q96">
-        <v>-0.06524571322992007</v>
+        <v>-0.07300151868981292</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5363046191963752</v>
+        <v>0.6344055430356506</v>
       </c>
       <c r="T96">
-        <v>11.32805125164839</v>
+        <v>13.59366150197808</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1019689145014633</v>
+        <v>0.100895557506711</v>
       </c>
       <c r="W96">
-        <v>0.211755729960555</v>
+        <v>0.2120088275399176</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3398963816715441</v>
+        <v>0.33631852502237</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9312,22 +9312,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2331286633147042</v>
+        <v>0.2350286633147042</v>
       </c>
       <c r="C97">
-        <v>-2.018893257421932</v>
+        <v>-2.077970681098301</v>
       </c>
       <c r="D97">
-        <v>1.835947277473335</v>
+        <v>1.823857648901128</v>
       </c>
       <c r="E97">
-        <v>3.065061024479196</v>
+        <v>3.112048819583357</v>
       </c>
       <c r="F97">
-        <v>4.463840534895268</v>
+        <v>4.510828329999429</v>
       </c>
       <c r="G97">
         <v>0.609</v>
@@ -9348,37 +9348,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M97">
-        <v>1.052573598128304</v>
+        <v>1.063653320213865</v>
       </c>
       <c r="N97">
-        <v>-0.6985735981283041</v>
+        <v>-0.7096533202138653</v>
       </c>
       <c r="O97">
-        <v>-0.2095720794384912</v>
+        <v>-0.2128959960641596</v>
       </c>
       <c r="P97">
-        <v>-0.4890015186898129</v>
+        <v>-0.4967573241497057</v>
       </c>
       <c r="Q97">
-        <v>-0.07300151868981292</v>
+        <v>-0.08075732414970577</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6344055430356506</v>
+        <v>0.7815569287945635</v>
       </c>
       <c r="T97">
-        <v>13.59366150197808</v>
+        <v>16.9920768774726</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.100895557506711</v>
+        <v>0.0998445621160161</v>
       </c>
       <c r="W97">
-        <v>0.2120088275399176</v>
+        <v>0.2122566522530434</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.33631852502237</v>
+        <v>0.332815207053387</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9394,22 +9394,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2350286633147042</v>
+        <v>0.2369286633147042</v>
       </c>
       <c r="C98">
-        <v>-2.0779706810983</v>
+        <v>-2.136889927068871</v>
       </c>
       <c r="D98">
-        <v>1.823857648901128</v>
+        <v>1.811926198034718</v>
       </c>
       <c r="E98">
-        <v>3.112048819583356</v>
+        <v>3.159036614687517</v>
       </c>
       <c r="F98">
-        <v>4.510828329999428</v>
+        <v>4.557816125103589</v>
       </c>
       <c r="G98">
         <v>0.609</v>
@@ -9430,37 +9430,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M98">
-        <v>1.063653320213865</v>
+        <v>1.074733042299426</v>
       </c>
       <c r="N98">
-        <v>-0.7096533202138651</v>
+        <v>-0.7207330422994263</v>
       </c>
       <c r="O98">
-        <v>-0.2128959960641595</v>
+        <v>-0.2162199126898279</v>
       </c>
       <c r="P98">
-        <v>-0.4967573241497055</v>
+        <v>-0.5045131296095984</v>
       </c>
       <c r="Q98">
-        <v>-0.08075732414970554</v>
+        <v>-0.0885131296095984</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7815569287945615</v>
+        <v>1.026809238392749</v>
       </c>
       <c r="T98">
-        <v>16.99207687747256</v>
+        <v>22.65610250329674</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09984456211601613</v>
+        <v>0.09881523673337678</v>
       </c>
       <c r="W98">
-        <v>0.2122566522530434</v>
+        <v>0.2124993671782698</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.332815207053387</v>
+        <v>0.3293841224445891</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9476,22 +9476,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2369286633147042</v>
+        <v>0.2388286633147041</v>
       </c>
       <c r="C99">
-        <v>-2.136889927068871</v>
+        <v>-2.195654079494333</v>
       </c>
       <c r="D99">
-        <v>1.811926198034718</v>
+        <v>1.800149840713416</v>
       </c>
       <c r="E99">
-        <v>3.159036614687517</v>
+        <v>3.206024409791678</v>
       </c>
       <c r="F99">
-        <v>4.557816125103589</v>
+        <v>4.60480392020775</v>
       </c>
       <c r="G99">
         <v>0.609</v>
@@ -9512,37 +9512,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M99">
-        <v>1.074733042299426</v>
+        <v>1.085812764384987</v>
       </c>
       <c r="N99">
-        <v>-0.7207330422994263</v>
+        <v>-0.7318127643849872</v>
       </c>
       <c r="O99">
-        <v>-0.2162199126898279</v>
+        <v>-0.2195438293154962</v>
       </c>
       <c r="P99">
-        <v>-0.5045131296095984</v>
+        <v>-0.5122689350694911</v>
       </c>
       <c r="Q99">
-        <v>-0.0885131296095984</v>
+        <v>-0.09626893506949113</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.026809238392749</v>
+        <v>1.517313857589123</v>
       </c>
       <c r="T99">
-        <v>22.65610250329674</v>
+        <v>33.98415375494511</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09881523673337678</v>
+        <v>0.09780691799119946</v>
       </c>
       <c r="W99">
-        <v>0.2124993671782698</v>
+        <v>0.2127371287376752</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3293841224445891</v>
+        <v>0.3260230599706648</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9558,22 +9558,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2388286633147041</v>
+        <v>0.2407286633147042</v>
       </c>
       <c r="C100">
-        <v>-2.195654079494333</v>
+        <v>-2.254266142872871</v>
       </c>
       <c r="D100">
-        <v>1.800149840713416</v>
+        <v>1.788525572439039</v>
       </c>
       <c r="E100">
-        <v>3.206024409791678</v>
+        <v>3.253012204895839</v>
       </c>
       <c r="F100">
-        <v>4.60480392020775</v>
+        <v>4.65179171531191</v>
       </c>
       <c r="G100">
         <v>0.609</v>
@@ -9594,37 +9594,37 @@
         <v>0.3540000000000001</v>
       </c>
       <c r="M100">
-        <v>1.085812764384987</v>
+        <v>1.096892486470548</v>
       </c>
       <c r="N100">
-        <v>-0.7318127643849872</v>
+        <v>-0.7428924864705484</v>
       </c>
       <c r="O100">
-        <v>-0.2195438293154962</v>
+        <v>-0.2228677459411645</v>
       </c>
       <c r="P100">
-        <v>-0.5122689350694911</v>
+        <v>-0.5200247405293839</v>
       </c>
       <c r="Q100">
-        <v>-0.09626893506949113</v>
+        <v>-0.1040247405293839</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.517313857589123</v>
+        <v>2.988827715178246</v>
       </c>
       <c r="T100">
-        <v>33.98415375494511</v>
+        <v>67.96830750989022</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09780691799119946</v>
+        <v>0.09681896932462168</v>
       </c>
       <c r="W100">
-        <v>0.2127371287376752</v>
+        <v>0.2129700870332542</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9632,91 +9632,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3260230599706648</v>
+        <v>0.3227298977487389</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2407286633147042</v>
-      </c>
-      <c r="C101">
-        <v>-2.254266142872871</v>
-      </c>
-      <c r="D101">
-        <v>1.788525572439039</v>
-      </c>
-      <c r="E101">
-        <v>3.253012204895839</v>
-      </c>
-      <c r="F101">
-        <v>4.65179171531191</v>
-      </c>
-      <c r="G101">
-        <v>0.609</v>
-      </c>
-      <c r="H101">
-        <v>3.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.7700000000000001</v>
-      </c>
-      <c r="K101">
-        <v>0.416</v>
-      </c>
-      <c r="L101">
-        <v>0.3540000000000001</v>
-      </c>
-      <c r="M101">
-        <v>1.096892486470548</v>
-      </c>
-      <c r="N101">
-        <v>-0.7428924864705484</v>
-      </c>
-      <c r="O101">
-        <v>-0.2228677459411645</v>
-      </c>
-      <c r="P101">
-        <v>-0.5200247405293839</v>
-      </c>
-      <c r="Q101">
-        <v>-0.1040247405293839</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.988827715178246</v>
-      </c>
-      <c r="T101">
-        <v>67.96830750989022</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09681896932462168</v>
-      </c>
-      <c r="W101">
-        <v>0.2129700870332542</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3227298977487389</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
